--- a/115 僑生A班.xlsx
+++ b/115 僑生A班.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE5A5CB-38C7-4361-9DF5-13F2D5C0186F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
     <sheet name="工作表3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>排名</t>
   </si>
@@ -156,14 +157,22 @@
   </si>
   <si>
     <t>自我介紹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0806</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龐文傑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -177,12 +186,6 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -220,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -228,39 +231,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -356,6 +341,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -391,6 +393,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -566,14 +585,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:II37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="5" width="6.5" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.25" bestFit="1" customWidth="1"/>
     <col min="15" max="19" width="5.75" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.875" bestFit="1" customWidth="1"/>
     <col min="22" max="29" width="4.875" bestFit="1" customWidth="1"/>
@@ -626,7 +646,7 @@
       </c>
       <c r="K1" s="2">
         <f t="shared" ref="K1:BV1" si="0">MIN(K3:K21)-1</f>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="L1" s="2">
         <f t="shared" si="0"/>
@@ -1390,17 +1410,21 @@
       <c r="J2" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="K2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:195" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1411,12 +1435,12 @@
         <v>60</v>
       </c>
       <c r="F3">
-        <f>RANK(G3,$G$3:$G$36)</f>
+        <f>RANK(G3,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H3">
         <v>40</v>
@@ -1425,6 +1449,9 @@
         <v>40</v>
       </c>
       <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
         <v>40</v>
       </c>
     </row>
@@ -1432,12 +1459,12 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" ref="C4:C22" si="3">SUM(H4:BR4)/63+60</f>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D22" si="4">SUM(BS4:EH4)/(131-63)+60</f>
@@ -1448,12 +1475,12 @@
         <v>60</v>
       </c>
       <c r="F4">
-        <f>RANK(G4,$G$3:$G$36)</f>
+        <f>RANK(G4,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G36" si="6">SUM(H4:AAB4)</f>
-        <v>120</v>
+        <f t="shared" ref="G4:G35" si="6">SUM(H4:AAB4)</f>
+        <v>160</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -1462,6 +1489,9 @@
         <v>40</v>
       </c>
       <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
         <v>40</v>
       </c>
     </row>
@@ -1469,12 +1499,12 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="4"/>
@@ -1485,12 +1515,12 @@
         <v>60</v>
       </c>
       <c r="F5">
-        <f>RANK(G5,$G$3:$G$36)</f>
+        <f>RANK(G5,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G5">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H5">
         <v>40</v>
@@ -1499,6 +1529,9 @@
         <v>40</v>
       </c>
       <c r="J5">
+        <v>40</v>
+      </c>
+      <c r="K5">
         <v>40</v>
       </c>
     </row>
@@ -1506,12 +1539,12 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="4"/>
@@ -1522,12 +1555,12 @@
         <v>60</v>
       </c>
       <c r="F6">
-        <f>RANK(G6,$G$3:$G$36)</f>
+        <f>RANK(G6,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G6">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H6">
         <v>40</v>
@@ -1536,6 +1569,9 @@
         <v>40</v>
       </c>
       <c r="J6">
+        <v>40</v>
+      </c>
+      <c r="K6">
         <v>40</v>
       </c>
     </row>
@@ -1543,12 +1579,12 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="4"/>
@@ -1559,12 +1595,12 @@
         <v>60</v>
       </c>
       <c r="F7">
-        <f>RANK(G7,$G$3:$G$36)</f>
+        <f>RANK(G7,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G7">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -1573,6 +1609,9 @@
         <v>40</v>
       </c>
       <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7">
         <v>40</v>
       </c>
     </row>
@@ -1580,12 +1619,12 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="4"/>
@@ -1596,12 +1635,12 @@
         <v>60</v>
       </c>
       <c r="F8">
-        <f>RANK(G8,$G$3:$G$36)</f>
+        <f>RANK(G8,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G8">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H8">
         <v>40</v>
@@ -1610,6 +1649,9 @@
         <v>40</v>
       </c>
       <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
         <v>40</v>
       </c>
     </row>
@@ -1617,12 +1659,12 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="4"/>
@@ -1633,12 +1675,12 @@
         <v>60</v>
       </c>
       <c r="F9">
-        <f>RANK(G9,$G$3:$G$36)</f>
+        <f>RANK(G9,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G9">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -1647,6 +1689,9 @@
         <v>40</v>
       </c>
       <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="K9">
         <v>40</v>
       </c>
     </row>
@@ -1654,12 +1699,12 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="4"/>
@@ -1670,12 +1715,12 @@
         <v>60</v>
       </c>
       <c r="F10">
-        <f>RANK(G10,$G$3:$G$36)</f>
+        <f>RANK(G10,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G10">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H10">
         <v>40</v>
@@ -1684,6 +1729,9 @@
         <v>40</v>
       </c>
       <c r="J10">
+        <v>40</v>
+      </c>
+      <c r="K10">
         <v>40</v>
       </c>
     </row>
@@ -1691,12 +1739,12 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="4"/>
@@ -1707,12 +1755,12 @@
         <v>60</v>
       </c>
       <c r="F11">
-        <f>RANK(G11,$G$3:$G$36)</f>
+        <f>RANK(G11,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G11">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -1721,6 +1769,9 @@
         <v>40</v>
       </c>
       <c r="J11">
+        <v>40</v>
+      </c>
+      <c r="K11">
         <v>40</v>
       </c>
     </row>
@@ -1728,12 +1779,12 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="4"/>
@@ -1744,12 +1795,12 @@
         <v>60</v>
       </c>
       <c r="F12">
-        <f>RANK(G12,$G$3:$G$36)</f>
+        <f>RANK(G12,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G12">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1758,6 +1809,9 @@
         <v>40</v>
       </c>
       <c r="J12">
+        <v>40</v>
+      </c>
+      <c r="K12">
         <v>40</v>
       </c>
     </row>
@@ -1765,12 +1819,12 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="4"/>
@@ -1781,12 +1835,12 @@
         <v>60</v>
       </c>
       <c r="F13">
-        <f>RANK(G13,$G$3:$G$36)</f>
+        <f>RANK(G13,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G13">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H13">
         <v>40</v>
@@ -1795,6 +1849,9 @@
         <v>40</v>
       </c>
       <c r="J13">
+        <v>40</v>
+      </c>
+      <c r="K13">
         <v>40</v>
       </c>
     </row>
@@ -1802,12 +1859,12 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="4"/>
@@ -1818,12 +1875,12 @@
         <v>60</v>
       </c>
       <c r="F14">
-        <f>RANK(G14,$G$3:$G$36)</f>
+        <f>RANK(G14,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G14">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -1832,6 +1889,9 @@
         <v>40</v>
       </c>
       <c r="J14">
+        <v>40</v>
+      </c>
+      <c r="K14">
         <v>40</v>
       </c>
     </row>
@@ -1839,12 +1899,12 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="4"/>
@@ -1855,12 +1915,12 @@
         <v>60</v>
       </c>
       <c r="F15">
-        <f>RANK(G15,$G$3:$G$36)</f>
+        <f>RANK(G15,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G15">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H15">
         <v>40</v>
@@ -1869,6 +1929,9 @@
         <v>40</v>
       </c>
       <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15">
         <v>40</v>
       </c>
     </row>
@@ -1876,12 +1939,12 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="4"/>
@@ -1892,12 +1955,12 @@
         <v>60</v>
       </c>
       <c r="F16">
-        <f>RANK(G16,$G$3:$G$36)</f>
+        <f>RANK(G16,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G16">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H16">
         <v>40</v>
@@ -1906,6 +1969,9 @@
         <v>40</v>
       </c>
       <c r="J16">
+        <v>40</v>
+      </c>
+      <c r="K16">
         <v>40</v>
       </c>
     </row>
@@ -1913,12 +1979,12 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="4"/>
@@ -1929,12 +1995,12 @@
         <v>60</v>
       </c>
       <c r="F17">
-        <f>RANK(G17,$G$3:$G$36)</f>
+        <f>RANK(G17,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G17">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -1943,6 +2009,9 @@
         <v>40</v>
       </c>
       <c r="J17">
+        <v>40</v>
+      </c>
+      <c r="K17">
         <v>40</v>
       </c>
     </row>
@@ -1950,12 +2019,12 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="4"/>
@@ -1966,12 +2035,12 @@
         <v>60</v>
       </c>
       <c r="F18">
-        <f>RANK(G18,$G$3:$G$36)</f>
+        <f>RANK(G18,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G18">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H18">
         <v>40</v>
@@ -1980,6 +2049,9 @@
         <v>40</v>
       </c>
       <c r="J18">
+        <v>40</v>
+      </c>
+      <c r="K18">
         <v>40</v>
       </c>
     </row>
@@ -1987,12 +2059,12 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="4"/>
@@ -2003,12 +2075,12 @@
         <v>60</v>
       </c>
       <c r="F19">
-        <f>RANK(G19,$G$3:$G$36)</f>
+        <f>RANK(G19,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G19">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -2017,6 +2089,9 @@
         <v>40</v>
       </c>
       <c r="J19">
+        <v>40</v>
+      </c>
+      <c r="K19">
         <v>40</v>
       </c>
     </row>
@@ -2024,12 +2099,12 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="4"/>
@@ -2040,12 +2115,12 @@
         <v>60</v>
       </c>
       <c r="F20">
-        <f>RANK(G20,$G$3:$G$36)</f>
+        <f>RANK(G20,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G20">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -2054,6 +2129,9 @@
         <v>40</v>
       </c>
       <c r="J20">
+        <v>40</v>
+      </c>
+      <c r="K20">
         <v>40</v>
       </c>
     </row>
@@ -2061,12 +2139,12 @@
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="4"/>
@@ -2077,12 +2155,12 @@
         <v>60</v>
       </c>
       <c r="F21">
-        <f>RANK(G21,$G$3:$G$36)</f>
+        <f>RANK(G21,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G21">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -2091,6 +2169,9 @@
         <v>40</v>
       </c>
       <c r="J21">
+        <v>40</v>
+      </c>
+      <c r="K21">
         <v>40</v>
       </c>
     </row>
@@ -2098,12 +2179,12 @@
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="3"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="4"/>
@@ -2114,12 +2195,12 @@
         <v>60</v>
       </c>
       <c r="F22">
-        <f>RANK(G22,$G$3:$G$36)</f>
+        <f>RANK(G22,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G22">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -2130,242 +2211,244 @@
       <c r="J22">
         <v>40</v>
       </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6"/>
-      <c r="AF22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="6"/>
-      <c r="AI22" s="6"/>
-      <c r="AJ22" s="6"/>
-      <c r="AK22" s="6"/>
-      <c r="AL22" s="6"/>
-      <c r="AM22" s="6"/>
-      <c r="AN22" s="6"/>
-      <c r="AO22" s="6"/>
-      <c r="AP22" s="6"/>
-      <c r="AQ22" s="6"/>
-      <c r="AR22" s="6"/>
-      <c r="AS22" s="6"/>
-      <c r="AT22" s="6"/>
-      <c r="AU22" s="6"/>
-      <c r="AV22" s="6"/>
-      <c r="AW22" s="6"/>
-      <c r="AX22" s="6"/>
-      <c r="AY22" s="6"/>
-      <c r="AZ22" s="6"/>
-      <c r="BA22" s="6"/>
-      <c r="BB22" s="6"/>
-      <c r="BC22" s="6"/>
-      <c r="BD22" s="6"/>
-      <c r="BE22" s="6"/>
-      <c r="BF22" s="6"/>
-      <c r="BG22" s="6"/>
-      <c r="BH22" s="6"/>
-      <c r="BI22" s="6"/>
-      <c r="BJ22" s="6"/>
-      <c r="BK22" s="6"/>
-      <c r="BL22" s="6"/>
-      <c r="BM22" s="6"/>
-      <c r="BN22" s="6"/>
-      <c r="BO22" s="6"/>
-      <c r="BP22" s="6"/>
-      <c r="BQ22" s="6"/>
-      <c r="BR22" s="6"/>
-      <c r="BS22" s="6"/>
-      <c r="BT22" s="6"/>
-      <c r="BU22" s="6"/>
-      <c r="BV22" s="6"/>
-      <c r="BW22" s="6"/>
-      <c r="BX22" s="6"/>
-      <c r="BY22" s="6"/>
-      <c r="BZ22" s="6"/>
-      <c r="CA22" s="6"/>
-      <c r="CB22" s="6"/>
-      <c r="CC22" s="6"/>
-      <c r="CD22" s="6"/>
-      <c r="CE22" s="6"/>
-      <c r="CF22" s="6"/>
-      <c r="CG22" s="6"/>
-      <c r="CH22" s="6"/>
-      <c r="CI22" s="6"/>
-      <c r="CJ22" s="6"/>
-      <c r="CK22" s="6"/>
-      <c r="CL22" s="6"/>
-      <c r="CM22" s="6"/>
-      <c r="CN22" s="6"/>
-      <c r="CO22" s="6"/>
-      <c r="CP22" s="6"/>
-      <c r="CQ22" s="6"/>
-      <c r="CR22" s="6"/>
-      <c r="CS22" s="6"/>
-      <c r="CT22" s="6"/>
-      <c r="CU22" s="6"/>
-      <c r="CV22" s="6"/>
-      <c r="CW22" s="6"/>
-      <c r="CX22" s="6"/>
-      <c r="CY22" s="6"/>
-      <c r="CZ22" s="6"/>
-      <c r="DA22" s="6"/>
-      <c r="DB22" s="6"/>
-      <c r="DC22" s="6"/>
-      <c r="DD22" s="6"/>
-      <c r="DE22" s="6"/>
-      <c r="DF22" s="6"/>
-      <c r="DG22" s="6"/>
-      <c r="DH22" s="6"/>
-      <c r="DI22" s="6"/>
-      <c r="DJ22" s="6"/>
-      <c r="DK22" s="6"/>
-      <c r="DL22" s="6"/>
-      <c r="DM22" s="6"/>
-      <c r="DN22" s="6"/>
-      <c r="DO22" s="6"/>
-      <c r="DP22" s="6"/>
-      <c r="DQ22" s="6"/>
-      <c r="DR22" s="6"/>
-      <c r="DS22" s="6"/>
-      <c r="DT22" s="6"/>
-      <c r="DU22" s="6"/>
-      <c r="DV22" s="6"/>
-      <c r="DW22" s="6"/>
-      <c r="DX22" s="6"/>
-      <c r="DY22" s="6"/>
-      <c r="DZ22" s="6"/>
-      <c r="EA22" s="6"/>
-      <c r="EB22" s="6"/>
-      <c r="EC22" s="6"/>
-      <c r="ED22" s="6"/>
-      <c r="EE22" s="6"/>
-      <c r="EF22" s="6"/>
-      <c r="EG22" s="6"/>
-      <c r="EH22" s="6"/>
-      <c r="EI22" s="6"/>
-      <c r="EJ22" s="6"/>
-      <c r="EK22" s="6"/>
-      <c r="EL22" s="6"/>
-      <c r="EM22" s="6"/>
-      <c r="EN22" s="6"/>
-      <c r="EO22" s="6"/>
-      <c r="EP22" s="6"/>
-      <c r="EQ22" s="6"/>
-      <c r="ER22" s="6"/>
-      <c r="ES22" s="6"/>
-      <c r="ET22" s="6"/>
-      <c r="EU22" s="6"/>
-      <c r="EV22" s="6"/>
-      <c r="EW22" s="6"/>
-      <c r="EX22" s="6"/>
-      <c r="EY22" s="6"/>
-      <c r="EZ22" s="6"/>
-      <c r="FA22" s="6"/>
-      <c r="FB22" s="6"/>
-      <c r="FC22" s="6"/>
-      <c r="FD22" s="6"/>
-      <c r="FE22" s="6"/>
-      <c r="FF22" s="6"/>
-      <c r="FG22" s="6"/>
-      <c r="FH22" s="6"/>
-      <c r="FI22" s="6"/>
-      <c r="FJ22" s="6"/>
-      <c r="FK22" s="6"/>
-      <c r="FL22" s="6"/>
-      <c r="FM22" s="6"/>
-      <c r="FN22" s="6"/>
-      <c r="FO22" s="6"/>
-      <c r="FP22" s="6"/>
-      <c r="FQ22" s="6"/>
-      <c r="FR22" s="6"/>
-      <c r="FS22" s="6"/>
-      <c r="FT22" s="6"/>
-      <c r="FU22" s="6"/>
-      <c r="FV22" s="6"/>
-      <c r="FW22" s="6"/>
-      <c r="FX22" s="6"/>
-      <c r="FY22" s="6"/>
-      <c r="FZ22" s="6"/>
-      <c r="GA22" s="6"/>
-      <c r="GB22" s="6"/>
-      <c r="GC22" s="6"/>
-      <c r="GD22" s="6"/>
-      <c r="GE22" s="6"/>
-      <c r="GF22" s="6"/>
-      <c r="GG22" s="6"/>
-      <c r="GH22" s="6"/>
-      <c r="GI22" s="6"/>
-      <c r="GJ22" s="6"/>
-      <c r="GK22" s="6"/>
-      <c r="GL22" s="6"/>
-      <c r="GM22" s="6"/>
-      <c r="GN22" s="6"/>
-      <c r="GO22" s="6"/>
-      <c r="GP22" s="6"/>
-      <c r="GQ22" s="6"/>
-      <c r="GR22" s="6"/>
-      <c r="GS22" s="6"/>
-      <c r="GT22" s="6"/>
-      <c r="GU22" s="6"/>
-      <c r="GV22" s="6"/>
-      <c r="GW22" s="6"/>
-      <c r="GX22" s="6"/>
-      <c r="GY22" s="6"/>
-      <c r="GZ22" s="6"/>
-      <c r="HA22" s="6"/>
-      <c r="HB22" s="6"/>
-      <c r="HC22" s="6"/>
-      <c r="HD22" s="6"/>
-      <c r="HE22" s="6"/>
-      <c r="HF22" s="6"/>
-      <c r="HG22" s="6"/>
-      <c r="HH22" s="6"/>
-      <c r="HI22" s="6"/>
-      <c r="HJ22" s="6"/>
-      <c r="HK22" s="6"/>
+      <c r="K22" s="5">
+        <v>40</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="5"/>
+      <c r="AH22" s="5"/>
+      <c r="AI22" s="5"/>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="5"/>
+      <c r="AL22" s="5"/>
+      <c r="AM22" s="5"/>
+      <c r="AN22" s="5"/>
+      <c r="AO22" s="5"/>
+      <c r="AP22" s="5"/>
+      <c r="AQ22" s="5"/>
+      <c r="AR22" s="5"/>
+      <c r="AS22" s="5"/>
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="5"/>
+      <c r="AV22" s="5"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="5"/>
+      <c r="AY22" s="5"/>
+      <c r="AZ22" s="5"/>
+      <c r="BA22" s="5"/>
+      <c r="BB22" s="5"/>
+      <c r="BC22" s="5"/>
+      <c r="BD22" s="5"/>
+      <c r="BE22" s="5"/>
+      <c r="BF22" s="5"/>
+      <c r="BG22" s="5"/>
+      <c r="BH22" s="5"/>
+      <c r="BI22" s="5"/>
+      <c r="BJ22" s="5"/>
+      <c r="BK22" s="5"/>
+      <c r="BL22" s="5"/>
+      <c r="BM22" s="5"/>
+      <c r="BN22" s="5"/>
+      <c r="BO22" s="5"/>
+      <c r="BP22" s="5"/>
+      <c r="BQ22" s="5"/>
+      <c r="BR22" s="5"/>
+      <c r="BS22" s="5"/>
+      <c r="BT22" s="5"/>
+      <c r="BU22" s="5"/>
+      <c r="BV22" s="5"/>
+      <c r="BW22" s="5"/>
+      <c r="BX22" s="5"/>
+      <c r="BY22" s="5"/>
+      <c r="BZ22" s="5"/>
+      <c r="CA22" s="5"/>
+      <c r="CB22" s="5"/>
+      <c r="CC22" s="5"/>
+      <c r="CD22" s="5"/>
+      <c r="CE22" s="5"/>
+      <c r="CF22" s="5"/>
+      <c r="CG22" s="5"/>
+      <c r="CH22" s="5"/>
+      <c r="CI22" s="5"/>
+      <c r="CJ22" s="5"/>
+      <c r="CK22" s="5"/>
+      <c r="CL22" s="5"/>
+      <c r="CM22" s="5"/>
+      <c r="CN22" s="5"/>
+      <c r="CO22" s="5"/>
+      <c r="CP22" s="5"/>
+      <c r="CQ22" s="5"/>
+      <c r="CR22" s="5"/>
+      <c r="CS22" s="5"/>
+      <c r="CT22" s="5"/>
+      <c r="CU22" s="5"/>
+      <c r="CV22" s="5"/>
+      <c r="CW22" s="5"/>
+      <c r="CX22" s="5"/>
+      <c r="CY22" s="5"/>
+      <c r="CZ22" s="5"/>
+      <c r="DA22" s="5"/>
+      <c r="DB22" s="5"/>
+      <c r="DC22" s="5"/>
+      <c r="DD22" s="5"/>
+      <c r="DE22" s="5"/>
+      <c r="DF22" s="5"/>
+      <c r="DG22" s="5"/>
+      <c r="DH22" s="5"/>
+      <c r="DI22" s="5"/>
+      <c r="DJ22" s="5"/>
+      <c r="DK22" s="5"/>
+      <c r="DL22" s="5"/>
+      <c r="DM22" s="5"/>
+      <c r="DN22" s="5"/>
+      <c r="DO22" s="5"/>
+      <c r="DP22" s="5"/>
+      <c r="DQ22" s="5"/>
+      <c r="DR22" s="5"/>
+      <c r="DS22" s="5"/>
+      <c r="DT22" s="5"/>
+      <c r="DU22" s="5"/>
+      <c r="DV22" s="5"/>
+      <c r="DW22" s="5"/>
+      <c r="DX22" s="5"/>
+      <c r="DY22" s="5"/>
+      <c r="DZ22" s="5"/>
+      <c r="EA22" s="5"/>
+      <c r="EB22" s="5"/>
+      <c r="EC22" s="5"/>
+      <c r="ED22" s="5"/>
+      <c r="EE22" s="5"/>
+      <c r="EF22" s="5"/>
+      <c r="EG22" s="5"/>
+      <c r="EH22" s="5"/>
+      <c r="EI22" s="5"/>
+      <c r="EJ22" s="5"/>
+      <c r="EK22" s="5"/>
+      <c r="EL22" s="5"/>
+      <c r="EM22" s="5"/>
+      <c r="EN22" s="5"/>
+      <c r="EO22" s="5"/>
+      <c r="EP22" s="5"/>
+      <c r="EQ22" s="5"/>
+      <c r="ER22" s="5"/>
+      <c r="ES22" s="5"/>
+      <c r="ET22" s="5"/>
+      <c r="EU22" s="5"/>
+      <c r="EV22" s="5"/>
+      <c r="EW22" s="5"/>
+      <c r="EX22" s="5"/>
+      <c r="EY22" s="5"/>
+      <c r="EZ22" s="5"/>
+      <c r="FA22" s="5"/>
+      <c r="FB22" s="5"/>
+      <c r="FC22" s="5"/>
+      <c r="FD22" s="5"/>
+      <c r="FE22" s="5"/>
+      <c r="FF22" s="5"/>
+      <c r="FG22" s="5"/>
+      <c r="FH22" s="5"/>
+      <c r="FI22" s="5"/>
+      <c r="FJ22" s="5"/>
+      <c r="FK22" s="5"/>
+      <c r="FL22" s="5"/>
+      <c r="FM22" s="5"/>
+      <c r="FN22" s="5"/>
+      <c r="FO22" s="5"/>
+      <c r="FP22" s="5"/>
+      <c r="FQ22" s="5"/>
+      <c r="FR22" s="5"/>
+      <c r="FS22" s="5"/>
+      <c r="FT22" s="5"/>
+      <c r="FU22" s="5"/>
+      <c r="FV22" s="5"/>
+      <c r="FW22" s="5"/>
+      <c r="FX22" s="5"/>
+      <c r="FY22" s="5"/>
+      <c r="FZ22" s="5"/>
+      <c r="GA22" s="5"/>
+      <c r="GB22" s="5"/>
+      <c r="GC22" s="5"/>
+      <c r="GD22" s="5"/>
+      <c r="GE22" s="5"/>
+      <c r="GF22" s="5"/>
+      <c r="GG22" s="5"/>
+      <c r="GH22" s="5"/>
+      <c r="GI22" s="5"/>
+      <c r="GJ22" s="5"/>
+      <c r="GK22" s="5"/>
+      <c r="GL22" s="5"/>
+      <c r="GM22" s="5"/>
+      <c r="GN22" s="5"/>
+      <c r="GO22" s="5"/>
+      <c r="GP22" s="5"/>
+      <c r="GQ22" s="5"/>
+      <c r="GR22" s="5"/>
+      <c r="GS22" s="5"/>
+      <c r="GT22" s="5"/>
+      <c r="GU22" s="5"/>
+      <c r="GV22" s="5"/>
+      <c r="GW22" s="5"/>
+      <c r="GX22" s="5"/>
+      <c r="GY22" s="5"/>
+      <c r="GZ22" s="5"/>
+      <c r="HA22" s="5"/>
+      <c r="HB22" s="5"/>
+      <c r="HC22" s="5"/>
+      <c r="HD22" s="5"/>
+      <c r="HE22" s="5"/>
+      <c r="HF22" s="5"/>
+      <c r="HG22" s="5"/>
+      <c r="HH22" s="5"/>
+      <c r="HI22" s="5"/>
+      <c r="HJ22" s="5"/>
+      <c r="HK22" s="5"/>
     </row>
     <row r="23" spans="1:219" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="4">
-        <f t="shared" ref="C23:C36" si="7">SUM(H23:BR23)/63+60</f>
-        <v>61.904761904761905</v>
+        <f t="shared" ref="C23:C35" si="7">SUM(H23:BR23)/63+60</f>
+        <v>62.539682539682538</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D23:D36" si="8">SUM(BS23:EH23)/(131-63)+60</f>
+        <f t="shared" ref="D23:D35" si="8">SUM(BS23:EH23)/(131-63)+60</f>
         <v>60</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E23:E36" si="9">SUM(EH23:FV23)/36+60</f>
+        <f t="shared" ref="E23:E35" si="9">SUM(EH23:FV23)/36+60</f>
         <v>60</v>
       </c>
       <c r="F23">
-        <f>RANK(G23,$G$3:$G$36)</f>
+        <f>RANK(G23,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G23">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -2374,6 +2457,9 @@
         <v>40</v>
       </c>
       <c r="J23">
+        <v>40</v>
+      </c>
+      <c r="K23" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2381,12 +2467,12 @@
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="8"/>
@@ -2397,12 +2483,12 @@
         <v>60</v>
       </c>
       <c r="F24">
-        <f>RANK(G24,$G$3:$G$36)</f>
+        <f>RANK(G24,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G24">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H24">
         <v>40</v>
@@ -2411,6 +2497,9 @@
         <v>40</v>
       </c>
       <c r="J24">
+        <v>40</v>
+      </c>
+      <c r="K24" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2418,12 +2507,12 @@
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="8"/>
@@ -2434,12 +2523,12 @@
         <v>60</v>
       </c>
       <c r="F25">
-        <f>RANK(G25,$G$3:$G$36)</f>
+        <f>RANK(G25,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G25">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H25">
         <v>40</v>
@@ -2448,6 +2537,9 @@
         <v>40</v>
       </c>
       <c r="J25">
+        <v>40</v>
+      </c>
+      <c r="K25" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2455,12 +2547,12 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="8"/>
@@ -2471,12 +2563,12 @@
         <v>60</v>
       </c>
       <c r="F26">
-        <f>RANK(G26,$G$3:$G$36)</f>
+        <f>RANK(G26,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G26">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H26">
         <v>40</v>
@@ -2485,6 +2577,9 @@
         <v>40</v>
       </c>
       <c r="J26">
+        <v>40</v>
+      </c>
+      <c r="K26" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2492,12 +2587,12 @@
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="8"/>
@@ -2508,12 +2603,12 @@
         <v>60</v>
       </c>
       <c r="F27">
-        <f>RANK(G27,$G$3:$G$36)</f>
+        <f>RANK(G27,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G27">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H27">
         <v>40</v>
@@ -2522,6 +2617,9 @@
         <v>40</v>
       </c>
       <c r="J27">
+        <v>40</v>
+      </c>
+      <c r="K27" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2529,12 +2627,12 @@
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="8"/>
@@ -2545,12 +2643,12 @@
         <v>60</v>
       </c>
       <c r="F28">
-        <f>RANK(G28,$G$3:$G$36)</f>
+        <f>RANK(G28,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G28">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H28">
         <v>40</v>
@@ -2559,6 +2657,9 @@
         <v>40</v>
       </c>
       <c r="J28">
+        <v>40</v>
+      </c>
+      <c r="K28" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2566,12 +2667,12 @@
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="8"/>
@@ -2582,12 +2683,12 @@
         <v>60</v>
       </c>
       <c r="F29">
-        <f>RANK(G29,$G$3:$G$36)</f>
+        <f>RANK(G29,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G29">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H29">
         <v>40</v>
@@ -2596,6 +2697,9 @@
         <v>40</v>
       </c>
       <c r="J29">
+        <v>40</v>
+      </c>
+      <c r="K29" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2603,12 +2707,12 @@
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="8"/>
@@ -2619,12 +2723,12 @@
         <v>60</v>
       </c>
       <c r="F30">
-        <f>RANK(G30,$G$3:$G$36)</f>
+        <f>RANK(G30,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G30">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -2633,6 +2737,9 @@
         <v>40</v>
       </c>
       <c r="J30">
+        <v>40</v>
+      </c>
+      <c r="K30" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2640,12 +2747,12 @@
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="8"/>
@@ -2656,12 +2763,12 @@
         <v>60</v>
       </c>
       <c r="F31">
-        <f>RANK(G31,$G$3:$G$36)</f>
+        <f>RANK(G31,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G31">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H31">
         <v>40</v>
@@ -2670,6 +2777,9 @@
         <v>40</v>
       </c>
       <c r="J31">
+        <v>40</v>
+      </c>
+      <c r="K31" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2677,12 +2787,12 @@
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="8"/>
@@ -2693,12 +2803,12 @@
         <v>60</v>
       </c>
       <c r="F32">
-        <f>RANK(G32,$G$3:$G$36)</f>
+        <f>RANK(G32,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G32">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H32">
         <v>40</v>
@@ -2707,6 +2817,9 @@
         <v>40</v>
       </c>
       <c r="J32">
+        <v>40</v>
+      </c>
+      <c r="K32" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2714,12 +2827,12 @@
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="8"/>
@@ -2730,12 +2843,12 @@
         <v>60</v>
       </c>
       <c r="F33">
-        <f>RANK(G33,$G$3:$G$36)</f>
+        <f>RANK(G33,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G33">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H33">
         <v>40</v>
@@ -2744,6 +2857,9 @@
         <v>40</v>
       </c>
       <c r="J33">
+        <v>40</v>
+      </c>
+      <c r="K33" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2751,12 +2867,12 @@
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="8"/>
@@ -2767,12 +2883,12 @@
         <v>60</v>
       </c>
       <c r="F34">
-        <f>RANK(G34,$G$3:$G$36)</f>
+        <f>RANK(G34,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G34">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H34">
         <v>40</v>
@@ -2783,17 +2899,20 @@
       <c r="J34">
         <v>40</v>
       </c>
+      <c r="K34" s="5">
+        <v>40</v>
+      </c>
     </row>
-    <row r="35" spans="1:243" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:243" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="4">
         <f t="shared" si="7"/>
-        <v>61.904761904761905</v>
+        <v>62.539682539682538</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="8"/>
@@ -2804,12 +2923,12 @@
         <v>60</v>
       </c>
       <c r="F35">
-        <f>RANK(G35,$G$3:$G$36)</f>
+        <f>RANK(G35,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G35">
         <f t="shared" si="6"/>
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="H35">
         <v>40</v>
@@ -2820,555 +2939,595 @@
       <c r="J35">
         <v>40</v>
       </c>
+      <c r="K35" s="5">
+        <v>40</v>
+      </c>
     </row>
-    <row r="36" spans="1:243" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="5"/>
-      <c r="G36" s="1">
-        <f>SUM(H36:AAB36)</f>
-        <v>16290</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
+    <row r="36" spans="1:243" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="4">
+        <f t="shared" ref="C36" si="10">SUM(H36:BR36)/63+60</f>
+        <v>62.539682539682538</v>
+      </c>
+      <c r="D36" s="4">
+        <f t="shared" ref="D36" si="11">SUM(BS36:EH36)/(131-63)+60</f>
+        <v>60</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36" si="12">SUM(EH36:FV36)/36+60</f>
+        <v>60</v>
+      </c>
+      <c r="F36">
+        <f>RANK(G36,$G$3:$G$37)</f>
         <v>2</v>
       </c>
-      <c r="J36" s="1">
-        <v>3</v>
-      </c>
-      <c r="K36" s="1">
-        <v>4</v>
-      </c>
-      <c r="L36" s="1">
-        <v>5</v>
-      </c>
-      <c r="M36" s="1">
-        <v>6</v>
-      </c>
-      <c r="N36" s="1">
-        <v>7</v>
-      </c>
-      <c r="O36" s="1">
-        <v>8</v>
-      </c>
-      <c r="P36" s="1">
-        <v>9</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>10</v>
-      </c>
-      <c r="R36" s="1">
-        <v>11</v>
-      </c>
-      <c r="S36" s="1">
-        <v>12</v>
-      </c>
-      <c r="T36" s="1">
-        <v>13</v>
-      </c>
-      <c r="U36" s="1">
-        <v>14</v>
-      </c>
-      <c r="V36" s="1">
-        <v>15</v>
-      </c>
-      <c r="W36" s="1">
-        <v>16</v>
-      </c>
-      <c r="X36" s="1">
-        <v>17</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>18</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>19</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>20</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>21</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>22</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>23</v>
-      </c>
-      <c r="AE36" s="1">
-        <v>24</v>
-      </c>
-      <c r="AF36" s="1">
-        <v>25</v>
-      </c>
-      <c r="AG36" s="1">
-        <v>26</v>
-      </c>
-      <c r="AH36" s="1">
-        <v>27</v>
-      </c>
-      <c r="AI36" s="1">
-        <v>28</v>
-      </c>
-      <c r="AJ36" s="1">
-        <v>29</v>
-      </c>
-      <c r="AK36" s="1">
-        <v>30</v>
-      </c>
-      <c r="AL36" s="1">
-        <v>31</v>
-      </c>
-      <c r="AM36" s="1">
-        <v>32</v>
-      </c>
-      <c r="AN36" s="1">
-        <v>33</v>
-      </c>
-      <c r="AO36" s="1">
-        <v>34</v>
-      </c>
-      <c r="AP36" s="1">
-        <v>35</v>
-      </c>
-      <c r="AQ36" s="1">
-        <v>36</v>
-      </c>
-      <c r="AR36" s="1">
-        <v>37</v>
-      </c>
-      <c r="AS36" s="1">
-        <v>38</v>
-      </c>
-      <c r="AT36" s="1">
-        <v>39</v>
-      </c>
-      <c r="AU36" s="1">
-        <v>40</v>
-      </c>
-      <c r="AV36" s="1">
-        <v>41</v>
-      </c>
-      <c r="AW36" s="1">
-        <v>42</v>
-      </c>
-      <c r="AX36" s="1">
-        <v>43</v>
-      </c>
-      <c r="AY36" s="1">
-        <v>44</v>
-      </c>
-      <c r="AZ36" s="1">
-        <v>45</v>
-      </c>
-      <c r="BA36" s="1">
-        <v>46</v>
-      </c>
-      <c r="BB36" s="1">
-        <v>47</v>
-      </c>
-      <c r="BC36" s="1">
-        <v>48</v>
-      </c>
-      <c r="BD36" s="1">
-        <v>49</v>
-      </c>
-      <c r="BE36" s="1">
-        <v>50</v>
-      </c>
-      <c r="BF36" s="1">
-        <v>51</v>
-      </c>
-      <c r="BG36" s="1">
-        <v>52</v>
-      </c>
-      <c r="BH36" s="1">
-        <v>53</v>
-      </c>
-      <c r="BI36" s="1">
-        <v>54</v>
-      </c>
-      <c r="BJ36" s="1">
-        <v>55</v>
-      </c>
-      <c r="BK36" s="1">
-        <v>56</v>
-      </c>
-      <c r="BL36" s="1">
-        <v>57</v>
-      </c>
-      <c r="BM36" s="1">
-        <v>58</v>
-      </c>
-      <c r="BN36" s="1">
-        <v>59</v>
-      </c>
-      <c r="BO36" s="1">
-        <v>60</v>
-      </c>
-      <c r="BP36" s="1">
-        <v>61</v>
-      </c>
-      <c r="BQ36" s="1">
-        <v>62</v>
-      </c>
-      <c r="BR36" s="1">
-        <v>63</v>
-      </c>
-      <c r="BS36" s="1">
-        <v>64</v>
-      </c>
-      <c r="BT36" s="1">
-        <v>65</v>
-      </c>
-      <c r="BU36" s="1">
-        <v>66</v>
-      </c>
-      <c r="BV36" s="1">
-        <v>67</v>
-      </c>
-      <c r="BW36" s="1">
-        <v>68</v>
-      </c>
-      <c r="BX36" s="1">
-        <v>69</v>
-      </c>
-      <c r="BY36" s="1">
-        <v>70</v>
-      </c>
-      <c r="BZ36" s="1">
-        <v>71</v>
-      </c>
-      <c r="CA36" s="1">
-        <v>72</v>
-      </c>
-      <c r="CB36" s="1">
-        <v>73</v>
-      </c>
-      <c r="CC36" s="1">
-        <v>74</v>
-      </c>
-      <c r="CD36" s="1">
-        <v>75</v>
-      </c>
-      <c r="CE36" s="1">
-        <v>76</v>
-      </c>
-      <c r="CF36" s="1">
-        <v>77</v>
-      </c>
-      <c r="CG36" s="1">
-        <v>78</v>
-      </c>
-      <c r="CH36" s="1">
-        <v>79</v>
-      </c>
-      <c r="CI36" s="1">
-        <v>80</v>
-      </c>
-      <c r="CJ36" s="1">
-        <v>81</v>
-      </c>
-      <c r="CK36" s="1">
-        <v>82</v>
-      </c>
-      <c r="CL36" s="1">
-        <v>83</v>
-      </c>
-      <c r="CM36" s="1">
-        <v>84</v>
-      </c>
-      <c r="CN36" s="1">
-        <v>85</v>
-      </c>
-      <c r="CO36" s="1">
-        <v>86</v>
-      </c>
-      <c r="CP36" s="1">
-        <v>87</v>
-      </c>
-      <c r="CQ36" s="1">
-        <v>88</v>
-      </c>
-      <c r="CR36" s="1">
-        <v>89</v>
-      </c>
-      <c r="CS36" s="1">
-        <v>90</v>
-      </c>
-      <c r="CT36" s="1">
-        <v>91</v>
-      </c>
-      <c r="CU36" s="1">
-        <v>92</v>
-      </c>
-      <c r="CV36" s="1">
-        <v>93</v>
-      </c>
-      <c r="CW36" s="1">
-        <v>94</v>
-      </c>
-      <c r="CX36" s="1">
-        <v>95</v>
-      </c>
-      <c r="CY36" s="1">
-        <v>96</v>
-      </c>
-      <c r="CZ36" s="1">
-        <v>97</v>
-      </c>
-      <c r="DA36" s="1">
-        <v>98</v>
-      </c>
-      <c r="DB36" s="1">
-        <v>99</v>
-      </c>
-      <c r="DC36" s="1">
-        <v>100</v>
-      </c>
-      <c r="DD36" s="1">
-        <v>101</v>
-      </c>
-      <c r="DE36" s="1">
-        <v>102</v>
-      </c>
-      <c r="DF36" s="1">
-        <v>103</v>
-      </c>
-      <c r="DG36" s="1">
-        <v>104</v>
-      </c>
-      <c r="DH36" s="1">
-        <v>105</v>
-      </c>
-      <c r="DI36" s="1">
-        <v>106</v>
-      </c>
-      <c r="DJ36" s="1">
-        <v>107</v>
-      </c>
-      <c r="DK36" s="1">
-        <v>108</v>
-      </c>
-      <c r="DL36" s="1">
-        <v>109</v>
-      </c>
-      <c r="DM36" s="1">
-        <v>110</v>
-      </c>
-      <c r="DN36" s="1">
-        <v>111</v>
-      </c>
-      <c r="DO36" s="1">
-        <v>112</v>
-      </c>
-      <c r="DP36" s="1">
-        <v>113</v>
-      </c>
-      <c r="DQ36" s="1">
-        <v>114</v>
-      </c>
-      <c r="DR36" s="1">
-        <v>115</v>
-      </c>
-      <c r="DS36" s="1">
-        <v>116</v>
-      </c>
-      <c r="DT36" s="1">
-        <v>117</v>
-      </c>
-      <c r="DU36" s="1">
-        <v>118</v>
-      </c>
-      <c r="DV36" s="1">
-        <v>119</v>
-      </c>
-      <c r="DW36" s="1">
-        <v>120</v>
-      </c>
-      <c r="DX36" s="1">
-        <v>121</v>
-      </c>
-      <c r="DY36" s="1">
-        <v>122</v>
-      </c>
-      <c r="DZ36" s="1">
-        <v>123</v>
-      </c>
-      <c r="EA36" s="1">
-        <v>124</v>
-      </c>
-      <c r="EB36" s="1">
-        <v>125</v>
-      </c>
-      <c r="EC36" s="1">
-        <v>126</v>
-      </c>
-      <c r="ED36" s="1">
-        <v>127</v>
-      </c>
-      <c r="EE36" s="1">
-        <v>128</v>
-      </c>
-      <c r="EF36" s="1">
-        <v>129</v>
-      </c>
-      <c r="EG36" s="1">
-        <v>130</v>
-      </c>
-      <c r="EH36" s="1">
-        <v>131</v>
-      </c>
-      <c r="EI36" s="1">
-        <v>132</v>
-      </c>
-      <c r="EJ36" s="1">
-        <v>133</v>
-      </c>
-      <c r="EK36" s="1">
-        <v>134</v>
-      </c>
-      <c r="EL36" s="1">
-        <v>135</v>
-      </c>
-      <c r="EM36" s="1">
-        <v>136</v>
-      </c>
-      <c r="EN36" s="1">
-        <v>137</v>
-      </c>
-      <c r="EO36" s="1">
-        <v>138</v>
-      </c>
-      <c r="EP36" s="1">
-        <v>139</v>
-      </c>
-      <c r="EQ36" s="1">
-        <v>140</v>
-      </c>
-      <c r="ER36" s="1">
-        <v>141</v>
-      </c>
-      <c r="ES36" s="1">
-        <v>142</v>
-      </c>
-      <c r="ET36" s="1">
-        <v>143</v>
-      </c>
-      <c r="EU36" s="1">
-        <v>144</v>
-      </c>
-      <c r="EV36" s="1">
-        <v>145</v>
-      </c>
-      <c r="EW36" s="1">
-        <v>146</v>
-      </c>
-      <c r="EX36" s="1">
-        <v>147</v>
-      </c>
-      <c r="EY36" s="1">
-        <v>148</v>
-      </c>
-      <c r="EZ36" s="1">
-        <v>149</v>
-      </c>
-      <c r="FA36" s="1">
-        <v>150</v>
-      </c>
-      <c r="FB36" s="1">
-        <v>151</v>
-      </c>
-      <c r="FC36" s="1">
-        <v>152</v>
-      </c>
-      <c r="FD36" s="1">
-        <v>153</v>
-      </c>
-      <c r="FE36" s="1">
-        <v>154</v>
-      </c>
-      <c r="FF36" s="1">
-        <v>155</v>
-      </c>
-      <c r="FG36" s="1">
-        <v>156</v>
-      </c>
-      <c r="FH36" s="1">
-        <v>157</v>
-      </c>
-      <c r="FI36" s="1">
-        <v>158</v>
-      </c>
-      <c r="FJ36" s="1">
-        <v>159</v>
-      </c>
-      <c r="FK36" s="1">
+      <c r="G36">
+        <f t="shared" ref="G36" si="13">SUM(H36:AAB36)</f>
         <v>160</v>
       </c>
-      <c r="FL36" s="1">
-        <v>161</v>
-      </c>
-      <c r="FM36" s="1">
-        <v>162</v>
-      </c>
-      <c r="FN36" s="1">
-        <v>163</v>
-      </c>
-      <c r="FO36" s="1">
-        <v>164</v>
-      </c>
-      <c r="FP36" s="1">
-        <v>165</v>
-      </c>
-      <c r="FQ36" s="1">
-        <v>166</v>
-      </c>
-      <c r="FR36" s="1">
-        <v>167</v>
-      </c>
-      <c r="FS36" s="1">
-        <v>168</v>
-      </c>
-      <c r="FT36" s="1">
-        <v>169</v>
-      </c>
-      <c r="FU36" s="1">
-        <v>170</v>
-      </c>
-      <c r="FV36" s="1">
-        <v>171</v>
-      </c>
-      <c r="FW36" s="1">
-        <v>172</v>
-      </c>
-      <c r="FX36" s="1">
-        <v>173</v>
-      </c>
-      <c r="FY36" s="1">
-        <v>174</v>
-      </c>
-      <c r="FZ36" s="1">
-        <v>175</v>
-      </c>
-      <c r="GA36" s="1">
-        <v>176</v>
-      </c>
-      <c r="GB36" s="1">
-        <v>177</v>
-      </c>
-      <c r="GC36" s="1">
-        <v>178</v>
-      </c>
-      <c r="GD36" s="1">
-        <v>179</v>
-      </c>
-      <c r="GE36" s="1">
-        <v>180</v>
+      <c r="H36">
+        <v>40</v>
+      </c>
+      <c r="I36">
+        <v>40</v>
+      </c>
+      <c r="J36">
+        <v>40</v>
+      </c>
+      <c r="K36" s="5">
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:243" x14ac:dyDescent="0.25">
+      <c r="G37" s="1">
+        <f>SUM(H37:AAB37)</f>
+        <v>16290</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2</v>
+      </c>
+      <c r="J37" s="1">
+        <v>3</v>
+      </c>
+      <c r="K37" s="1">
+        <v>4</v>
+      </c>
+      <c r="L37" s="1">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1">
+        <v>6</v>
+      </c>
+      <c r="N37" s="1">
+        <v>7</v>
+      </c>
+      <c r="O37" s="1">
+        <v>8</v>
+      </c>
+      <c r="P37" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>10</v>
+      </c>
+      <c r="R37" s="1">
+        <v>11</v>
+      </c>
+      <c r="S37" s="1">
+        <v>12</v>
+      </c>
+      <c r="T37" s="1">
+        <v>13</v>
+      </c>
+      <c r="U37" s="1">
+        <v>14</v>
+      </c>
+      <c r="V37" s="1">
+        <v>15</v>
+      </c>
+      <c r="W37" s="1">
+        <v>16</v>
+      </c>
+      <c r="X37" s="1">
+        <v>17</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>18</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>19</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>20</v>
+      </c>
+      <c r="AB37" s="1">
+        <v>21</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>22</v>
+      </c>
+      <c r="AD37" s="1">
+        <v>23</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>24</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>25</v>
+      </c>
+      <c r="AG37" s="1">
+        <v>26</v>
+      </c>
+      <c r="AH37" s="1">
+        <v>27</v>
+      </c>
+      <c r="AI37" s="1">
+        <v>28</v>
+      </c>
+      <c r="AJ37" s="1">
+        <v>29</v>
+      </c>
+      <c r="AK37" s="1">
+        <v>30</v>
+      </c>
+      <c r="AL37" s="1">
+        <v>31</v>
+      </c>
+      <c r="AM37" s="1">
+        <v>32</v>
+      </c>
+      <c r="AN37" s="1">
+        <v>33</v>
+      </c>
+      <c r="AO37" s="1">
+        <v>34</v>
+      </c>
+      <c r="AP37" s="1">
+        <v>35</v>
+      </c>
+      <c r="AQ37" s="1">
+        <v>36</v>
+      </c>
+      <c r="AR37" s="1">
+        <v>37</v>
+      </c>
+      <c r="AS37" s="1">
+        <v>38</v>
+      </c>
+      <c r="AT37" s="1">
+        <v>39</v>
+      </c>
+      <c r="AU37" s="1">
+        <v>40</v>
+      </c>
+      <c r="AV37" s="1">
+        <v>41</v>
+      </c>
+      <c r="AW37" s="1">
+        <v>42</v>
+      </c>
+      <c r="AX37" s="1">
+        <v>43</v>
+      </c>
+      <c r="AY37" s="1">
+        <v>44</v>
+      </c>
+      <c r="AZ37" s="1">
+        <v>45</v>
+      </c>
+      <c r="BA37" s="1">
+        <v>46</v>
+      </c>
+      <c r="BB37" s="1">
+        <v>47</v>
+      </c>
+      <c r="BC37" s="1">
+        <v>48</v>
+      </c>
+      <c r="BD37" s="1">
+        <v>49</v>
+      </c>
+      <c r="BE37" s="1">
+        <v>50</v>
+      </c>
+      <c r="BF37" s="1">
+        <v>51</v>
+      </c>
+      <c r="BG37" s="1">
+        <v>52</v>
+      </c>
+      <c r="BH37" s="1">
+        <v>53</v>
+      </c>
+      <c r="BI37" s="1">
+        <v>54</v>
+      </c>
+      <c r="BJ37" s="1">
+        <v>55</v>
+      </c>
+      <c r="BK37" s="1">
+        <v>56</v>
+      </c>
+      <c r="BL37" s="1">
+        <v>57</v>
+      </c>
+      <c r="BM37" s="1">
+        <v>58</v>
+      </c>
+      <c r="BN37" s="1">
+        <v>59</v>
+      </c>
+      <c r="BO37" s="1">
+        <v>60</v>
+      </c>
+      <c r="BP37" s="1">
+        <v>61</v>
+      </c>
+      <c r="BQ37" s="1">
+        <v>62</v>
+      </c>
+      <c r="BR37" s="1">
+        <v>63</v>
+      </c>
+      <c r="BS37" s="1">
+        <v>64</v>
+      </c>
+      <c r="BT37" s="1">
+        <v>65</v>
+      </c>
+      <c r="BU37" s="1">
+        <v>66</v>
+      </c>
+      <c r="BV37" s="1">
+        <v>67</v>
+      </c>
+      <c r="BW37" s="1">
+        <v>68</v>
+      </c>
+      <c r="BX37" s="1">
+        <v>69</v>
+      </c>
+      <c r="BY37" s="1">
+        <v>70</v>
+      </c>
+      <c r="BZ37" s="1">
+        <v>71</v>
+      </c>
+      <c r="CA37" s="1">
+        <v>72</v>
+      </c>
+      <c r="CB37" s="1">
+        <v>73</v>
+      </c>
+      <c r="CC37" s="1">
+        <v>74</v>
+      </c>
+      <c r="CD37" s="1">
+        <v>75</v>
+      </c>
+      <c r="CE37" s="1">
+        <v>76</v>
+      </c>
+      <c r="CF37" s="1">
+        <v>77</v>
+      </c>
+      <c r="CG37" s="1">
+        <v>78</v>
+      </c>
+      <c r="CH37" s="1">
+        <v>79</v>
+      </c>
+      <c r="CI37" s="1">
+        <v>80</v>
+      </c>
+      <c r="CJ37" s="1">
+        <v>81</v>
+      </c>
+      <c r="CK37" s="1">
+        <v>82</v>
+      </c>
+      <c r="CL37" s="1">
+        <v>83</v>
+      </c>
+      <c r="CM37" s="1">
+        <v>84</v>
+      </c>
+      <c r="CN37" s="1">
+        <v>85</v>
+      </c>
+      <c r="CO37" s="1">
+        <v>86</v>
+      </c>
+      <c r="CP37" s="1">
+        <v>87</v>
+      </c>
+      <c r="CQ37" s="1">
+        <v>88</v>
+      </c>
+      <c r="CR37" s="1">
+        <v>89</v>
+      </c>
+      <c r="CS37" s="1">
+        <v>90</v>
+      </c>
+      <c r="CT37" s="1">
+        <v>91</v>
+      </c>
+      <c r="CU37" s="1">
+        <v>92</v>
+      </c>
+      <c r="CV37" s="1">
+        <v>93</v>
+      </c>
+      <c r="CW37" s="1">
+        <v>94</v>
+      </c>
+      <c r="CX37" s="1">
+        <v>95</v>
+      </c>
+      <c r="CY37" s="1">
+        <v>96</v>
+      </c>
+      <c r="CZ37" s="1">
+        <v>97</v>
+      </c>
+      <c r="DA37" s="1">
+        <v>98</v>
+      </c>
+      <c r="DB37" s="1">
+        <v>99</v>
+      </c>
+      <c r="DC37" s="1">
+        <v>100</v>
+      </c>
+      <c r="DD37" s="1">
+        <v>101</v>
+      </c>
+      <c r="DE37" s="1">
+        <v>102</v>
+      </c>
+      <c r="DF37" s="1">
+        <v>103</v>
+      </c>
+      <c r="DG37" s="1">
+        <v>104</v>
+      </c>
+      <c r="DH37" s="1">
+        <v>105</v>
+      </c>
+      <c r="DI37" s="1">
+        <v>106</v>
+      </c>
+      <c r="DJ37" s="1">
+        <v>107</v>
+      </c>
+      <c r="DK37" s="1">
+        <v>108</v>
+      </c>
+      <c r="DL37" s="1">
+        <v>109</v>
+      </c>
+      <c r="DM37" s="1">
+        <v>110</v>
+      </c>
+      <c r="DN37" s="1">
+        <v>111</v>
+      </c>
+      <c r="DO37" s="1">
+        <v>112</v>
+      </c>
+      <c r="DP37" s="1">
+        <v>113</v>
+      </c>
+      <c r="DQ37" s="1">
+        <v>114</v>
+      </c>
+      <c r="DR37" s="1">
+        <v>115</v>
+      </c>
+      <c r="DS37" s="1">
+        <v>116</v>
+      </c>
+      <c r="DT37" s="1">
+        <v>117</v>
+      </c>
+      <c r="DU37" s="1">
+        <v>118</v>
+      </c>
+      <c r="DV37" s="1">
+        <v>119</v>
+      </c>
+      <c r="DW37" s="1">
+        <v>120</v>
+      </c>
+      <c r="DX37" s="1">
+        <v>121</v>
+      </c>
+      <c r="DY37" s="1">
+        <v>122</v>
+      </c>
+      <c r="DZ37" s="1">
+        <v>123</v>
+      </c>
+      <c r="EA37" s="1">
+        <v>124</v>
+      </c>
+      <c r="EB37" s="1">
+        <v>125</v>
+      </c>
+      <c r="EC37" s="1">
+        <v>126</v>
+      </c>
+      <c r="ED37" s="1">
+        <v>127</v>
+      </c>
+      <c r="EE37" s="1">
+        <v>128</v>
+      </c>
+      <c r="EF37" s="1">
+        <v>129</v>
+      </c>
+      <c r="EG37" s="1">
+        <v>130</v>
+      </c>
+      <c r="EH37" s="1">
+        <v>131</v>
+      </c>
+      <c r="EI37" s="1">
+        <v>132</v>
+      </c>
+      <c r="EJ37" s="1">
+        <v>133</v>
+      </c>
+      <c r="EK37" s="1">
+        <v>134</v>
+      </c>
+      <c r="EL37" s="1">
+        <v>135</v>
+      </c>
+      <c r="EM37" s="1">
+        <v>136</v>
+      </c>
+      <c r="EN37" s="1">
+        <v>137</v>
+      </c>
+      <c r="EO37" s="1">
+        <v>138</v>
+      </c>
+      <c r="EP37" s="1">
+        <v>139</v>
+      </c>
+      <c r="EQ37" s="1">
+        <v>140</v>
+      </c>
+      <c r="ER37" s="1">
+        <v>141</v>
+      </c>
+      <c r="ES37" s="1">
+        <v>142</v>
+      </c>
+      <c r="ET37" s="1">
+        <v>143</v>
+      </c>
+      <c r="EU37" s="1">
+        <v>144</v>
+      </c>
+      <c r="EV37" s="1">
+        <v>145</v>
+      </c>
+      <c r="EW37" s="1">
+        <v>146</v>
+      </c>
+      <c r="EX37" s="1">
+        <v>147</v>
+      </c>
+      <c r="EY37" s="1">
+        <v>148</v>
+      </c>
+      <c r="EZ37" s="1">
+        <v>149</v>
+      </c>
+      <c r="FA37" s="1">
+        <v>150</v>
+      </c>
+      <c r="FB37" s="1">
+        <v>151</v>
+      </c>
+      <c r="FC37" s="1">
+        <v>152</v>
+      </c>
+      <c r="FD37" s="1">
+        <v>153</v>
+      </c>
+      <c r="FE37" s="1">
+        <v>154</v>
+      </c>
+      <c r="FF37" s="1">
+        <v>155</v>
+      </c>
+      <c r="FG37" s="1">
+        <v>156</v>
+      </c>
+      <c r="FH37" s="1">
+        <v>157</v>
+      </c>
+      <c r="FI37" s="1">
+        <v>158</v>
+      </c>
+      <c r="FJ37" s="1">
+        <v>159</v>
+      </c>
+      <c r="FK37" s="1">
+        <v>160</v>
+      </c>
+      <c r="FL37" s="1">
+        <v>161</v>
+      </c>
+      <c r="FM37" s="1">
+        <v>162</v>
+      </c>
+      <c r="FN37" s="1">
+        <v>163</v>
+      </c>
+      <c r="FO37" s="1">
+        <v>164</v>
+      </c>
+      <c r="FP37" s="1">
+        <v>165</v>
+      </c>
+      <c r="FQ37" s="1">
+        <v>166</v>
+      </c>
+      <c r="FR37" s="1">
+        <v>167</v>
+      </c>
+      <c r="FS37" s="1">
+        <v>168</v>
+      </c>
+      <c r="FT37" s="1">
+        <v>169</v>
+      </c>
+      <c r="FU37" s="1">
+        <v>170</v>
+      </c>
+      <c r="FV37" s="1">
+        <v>171</v>
+      </c>
+      <c r="FW37" s="1">
+        <v>172</v>
+      </c>
+      <c r="FX37" s="1">
+        <v>173</v>
+      </c>
+      <c r="FY37" s="1">
+        <v>174</v>
+      </c>
+      <c r="FZ37" s="1">
+        <v>175</v>
+      </c>
+      <c r="GA37" s="1">
+        <v>176</v>
+      </c>
+      <c r="GB37" s="1">
+        <v>177</v>
+      </c>
+      <c r="GC37" s="1">
+        <v>178</v>
+      </c>
+      <c r="GD37" s="1">
+        <v>179</v>
+      </c>
+      <c r="GE37" s="1">
+        <v>180</v>
+      </c>
       <c r="GF37" s="1"/>
       <c r="GG37" s="1"/>
       <c r="GH37" s="1"/>
@@ -3428,7 +3587,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="G3:G35">
+  <conditionalFormatting sqref="G3:G36">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -3442,7 +3601,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:QB21 H3:QB3 H4:J35">
+  <conditionalFormatting sqref="K4:QB21 H3:QB3 H4:J36 K22:K36">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -3492,7 +3651,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G3:G35</xm:sqref>
+          <xm:sqref>G3:G36</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3501,7 +3660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -3511,7 +3670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/115 僑生A班.xlsx
+++ b/115 僑生A班.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE5A5CB-38C7-4361-9DF5-13F2D5C0186F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1524EF83-A700-449D-8891-336C02283850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>排名</t>
   </si>
@@ -165,6 +165,14 @@
   </si>
   <si>
     <t>龐文傑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中打聽寫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0807</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -235,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -248,6 +256,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -649,11 +658,11 @@
         <v>39</v>
       </c>
       <c r="L1" s="2">
-        <f t="shared" si="0"/>
-        <v>-1</v>
+        <f>MIN(L3:L36)-1</f>
+        <v>39</v>
       </c>
       <c r="M1" s="2">
-        <f t="shared" si="0"/>
+        <f>MIN(N3:N21)-1</f>
         <v>-1</v>
       </c>
       <c r="N1" s="2">
@@ -1413,7 +1422,12 @@
       <c r="K2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="3" spans="1:195" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1424,7 +1438,7 @@
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>62.539682539682538</v>
+        <v>63.80952380952381</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1435,12 +1449,12 @@
         <v>60</v>
       </c>
       <c r="F3">
-        <f>RANK(G3,$G$3:$G$37)</f>
+        <f t="shared" ref="F3:F36" si="3">RANK(G3,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H3">
         <v>40</v>
@@ -1452,6 +1466,12 @@
         <v>40</v>
       </c>
       <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>40</v>
+      </c>
+      <c r="M3">
         <v>40</v>
       </c>
     </row>
@@ -1463,24 +1483,24 @@
         <v>7</v>
       </c>
       <c r="C4" s="4">
-        <f t="shared" ref="C4:C22" si="3">SUM(H4:BR4)/63+60</f>
-        <v>62.539682539682538</v>
+        <f t="shared" ref="C4:C22" si="4">SUM(H4:BR4)/63+60</f>
+        <v>63.492063492063494</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:D22" si="4">SUM(BS4:EH4)/(131-63)+60</f>
+        <f t="shared" ref="D4:D22" si="5">SUM(BS4:EH4)/(131-63)+60</f>
         <v>60</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="E4:E22" si="5">SUM(EH4:FV4)/36+60</f>
+        <f t="shared" ref="E4:E22" si="6">SUM(EH4:FV4)/36+60</f>
         <v>60</v>
       </c>
       <c r="F4">
-        <f>RANK(G4,$G$3:$G$37)</f>
-        <v>2</v>
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G35" si="6">SUM(H4:AAB4)</f>
-        <v>160</v>
+        <f t="shared" ref="G4:G35" si="7">SUM(H4:AAB4)</f>
+        <v>220</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -1493,6 +1513,12 @@
       </c>
       <c r="K4">
         <v>40</v>
+      </c>
+      <c r="L4">
+        <v>40</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:195" x14ac:dyDescent="0.25">
@@ -1503,24 +1529,24 @@
         <v>8</v>
       </c>
       <c r="C5" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F5">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D5" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E5" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F5">
-        <f>RANK(G5,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G5">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H5">
         <v>40</v>
@@ -1532,6 +1558,12 @@
         <v>40</v>
       </c>
       <c r="K5">
+        <v>40</v>
+      </c>
+      <c r="L5">
+        <v>40</v>
+      </c>
+      <c r="M5">
         <v>40</v>
       </c>
     </row>
@@ -1543,24 +1575,24 @@
         <v>9</v>
       </c>
       <c r="C6" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F6">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D6" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E6" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F6">
-        <f>RANK(G6,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G6">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H6">
         <v>40</v>
@@ -1572,6 +1604,12 @@
         <v>40</v>
       </c>
       <c r="K6">
+        <v>40</v>
+      </c>
+      <c r="L6">
+        <v>40</v>
+      </c>
+      <c r="M6">
         <v>40</v>
       </c>
     </row>
@@ -1583,24 +1621,24 @@
         <v>10</v>
       </c>
       <c r="C7" s="4">
+        <f t="shared" si="4"/>
+        <v>63.492063492063494</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F7">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D7" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E7" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F7">
-        <f>RANK(G7,$G$3:$G$37)</f>
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>220</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -1613,6 +1651,12 @@
       </c>
       <c r="K7">
         <v>40</v>
+      </c>
+      <c r="L7">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:195" x14ac:dyDescent="0.25">
@@ -1623,24 +1667,24 @@
         <v>11</v>
       </c>
       <c r="C8" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F8">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D8" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F8">
-        <f>RANK(G8,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G8">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H8">
         <v>40</v>
@@ -1652,6 +1696,12 @@
         <v>40</v>
       </c>
       <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>40</v>
+      </c>
+      <c r="M8">
         <v>40</v>
       </c>
     </row>
@@ -1663,24 +1713,24 @@
         <v>12</v>
       </c>
       <c r="C9" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F9">
-        <f>RANK(G9,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G9">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -1692,6 +1742,12 @@
         <v>40</v>
       </c>
       <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
+      </c>
+      <c r="M9">
         <v>40</v>
       </c>
     </row>
@@ -1703,24 +1759,24 @@
         <v>13</v>
       </c>
       <c r="C10" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E10" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F10">
-        <f>RANK(G10,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G10">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H10">
         <v>40</v>
@@ -1732,6 +1788,12 @@
         <v>40</v>
       </c>
       <c r="K10">
+        <v>40</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
         <v>40</v>
       </c>
     </row>
@@ -1743,24 +1805,24 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E11" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F11">
-        <f>RANK(G11,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G11">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -1772,6 +1834,12 @@
         <v>40</v>
       </c>
       <c r="K11">
+        <v>40</v>
+      </c>
+      <c r="L11">
+        <v>40</v>
+      </c>
+      <c r="M11">
         <v>40</v>
       </c>
     </row>
@@ -1783,24 +1851,24 @@
         <v>15</v>
       </c>
       <c r="C12" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D12" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E12" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F12">
-        <f>RANK(G12,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G12">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1812,6 +1880,12 @@
         <v>40</v>
       </c>
       <c r="K12">
+        <v>40</v>
+      </c>
+      <c r="L12">
+        <v>40</v>
+      </c>
+      <c r="M12">
         <v>40</v>
       </c>
     </row>
@@ -1823,24 +1897,24 @@
         <v>16</v>
       </c>
       <c r="C13" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D13" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F13">
-        <f>RANK(G13,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G13">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H13">
         <v>40</v>
@@ -1852,6 +1926,12 @@
         <v>40</v>
       </c>
       <c r="K13">
+        <v>40</v>
+      </c>
+      <c r="L13">
+        <v>40</v>
+      </c>
+      <c r="M13">
         <v>40</v>
       </c>
     </row>
@@ -1863,24 +1943,24 @@
         <v>17</v>
       </c>
       <c r="C14" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D14" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E14" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F14">
-        <f>RANK(G14,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G14">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -1892,6 +1972,12 @@
         <v>40</v>
       </c>
       <c r="K14">
+        <v>40</v>
+      </c>
+      <c r="L14">
+        <v>40</v>
+      </c>
+      <c r="M14">
         <v>40</v>
       </c>
     </row>
@@ -1903,24 +1989,24 @@
         <v>18</v>
       </c>
       <c r="C15" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D15" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E15" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F15">
-        <f>RANK(G15,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G15">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H15">
         <v>40</v>
@@ -1932,6 +2018,12 @@
         <v>40</v>
       </c>
       <c r="K15">
+        <v>40</v>
+      </c>
+      <c r="L15">
+        <v>40</v>
+      </c>
+      <c r="M15">
         <v>40</v>
       </c>
     </row>
@@ -1943,24 +2035,24 @@
         <v>19</v>
       </c>
       <c r="C16" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D16" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D16" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E16" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F16">
-        <f>RANK(G16,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G16">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H16">
         <v>40</v>
@@ -1972,6 +2064,12 @@
         <v>40</v>
       </c>
       <c r="K16">
+        <v>40</v>
+      </c>
+      <c r="L16">
+        <v>40</v>
+      </c>
+      <c r="M16">
         <v>40</v>
       </c>
     </row>
@@ -1983,24 +2081,24 @@
         <v>20</v>
       </c>
       <c r="C17" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D17" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F17">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D17" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E17" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F17">
-        <f>RANK(G17,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G17">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -2012,6 +2110,12 @@
         <v>40</v>
       </c>
       <c r="K17">
+        <v>40</v>
+      </c>
+      <c r="L17">
+        <v>40</v>
+      </c>
+      <c r="M17">
         <v>40</v>
       </c>
     </row>
@@ -2023,24 +2127,24 @@
         <v>21</v>
       </c>
       <c r="C18" s="4">
+        <f t="shared" si="4"/>
+        <v>63.492063492063494</v>
+      </c>
+      <c r="D18" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F18">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D18" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E18" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F18">
-        <f>RANK(G18,$G$3:$G$37)</f>
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>220</v>
       </c>
       <c r="H18">
         <v>40</v>
@@ -2053,6 +2157,12 @@
       </c>
       <c r="K18">
         <v>40</v>
+      </c>
+      <c r="L18">
+        <v>40</v>
+      </c>
+      <c r="M18">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:219" x14ac:dyDescent="0.25">
@@ -2063,24 +2173,24 @@
         <v>22</v>
       </c>
       <c r="C19" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D19" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D19" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E19" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F19">
-        <f>RANK(G19,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G19">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -2092,6 +2202,12 @@
         <v>40</v>
       </c>
       <c r="K19">
+        <v>40</v>
+      </c>
+      <c r="L19">
+        <v>40</v>
+      </c>
+      <c r="M19">
         <v>40</v>
       </c>
     </row>
@@ -2103,24 +2219,24 @@
         <v>23</v>
       </c>
       <c r="C20" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D20" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D20" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E20" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F20">
-        <f>RANK(G20,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G20">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -2132,6 +2248,12 @@
         <v>40</v>
       </c>
       <c r="K20">
+        <v>40</v>
+      </c>
+      <c r="L20">
+        <v>40</v>
+      </c>
+      <c r="M20">
         <v>40</v>
       </c>
     </row>
@@ -2143,24 +2265,24 @@
         <v>24</v>
       </c>
       <c r="C21" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D21" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D21" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E21" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F21">
-        <f>RANK(G21,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G21">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -2172,6 +2294,12 @@
         <v>40</v>
       </c>
       <c r="K21">
+        <v>40</v>
+      </c>
+      <c r="L21">
+        <v>40</v>
+      </c>
+      <c r="M21">
         <v>40</v>
       </c>
     </row>
@@ -2183,24 +2311,24 @@
         <v>25</v>
       </c>
       <c r="C22" s="4">
+        <f t="shared" si="4"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D22" s="4">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="3"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D22" s="4">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="E22" s="4">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="F22">
-        <f>RANK(G22,$G$3:$G$37)</f>
         <v>2</v>
       </c>
       <c r="G22">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -2214,8 +2342,12 @@
       <c r="K22" s="5">
         <v>40</v>
       </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="L22">
+        <v>40</v>
+      </c>
+      <c r="M22" s="5">
+        <v>40</v>
+      </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
@@ -2431,24 +2563,24 @@
         <v>26</v>
       </c>
       <c r="C23" s="4">
-        <f t="shared" ref="C23:C35" si="7">SUM(H23:BR23)/63+60</f>
-        <v>62.539682539682538</v>
+        <f t="shared" ref="C23:C35" si="8">SUM(H23:BR23)/63+60</f>
+        <v>63.80952380952381</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" ref="D23:D35" si="8">SUM(BS23:EH23)/(131-63)+60</f>
+        <f t="shared" ref="D23:D35" si="9">SUM(BS23:EH23)/(131-63)+60</f>
         <v>60</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E23:E35" si="9">SUM(EH23:FV23)/36+60</f>
+        <f t="shared" ref="E23:E35" si="10">SUM(EH23:FV23)/36+60</f>
         <v>60</v>
       </c>
       <c r="F23">
-        <f>RANK(G23,$G$3:$G$37)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="G23">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <f t="shared" si="7"/>
+        <v>240</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -2460,6 +2592,12 @@
         <v>40</v>
       </c>
       <c r="K23" s="5">
+        <v>40</v>
+      </c>
+      <c r="L23">
+        <v>40</v>
+      </c>
+      <c r="M23" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2471,24 +2609,24 @@
         <v>27</v>
       </c>
       <c r="C24" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D24" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D24" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E24" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F24">
-        <f>RANK(G24,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H24">
         <v>40</v>
@@ -2500,6 +2638,12 @@
         <v>40</v>
       </c>
       <c r="K24" s="5">
+        <v>40</v>
+      </c>
+      <c r="L24">
+        <v>40</v>
+      </c>
+      <c r="M24" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2511,24 +2655,24 @@
         <v>28</v>
       </c>
       <c r="C25" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D25" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D25" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E25" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F25">
-        <f>RANK(G25,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H25">
         <v>40</v>
@@ -2540,6 +2684,12 @@
         <v>40</v>
       </c>
       <c r="K25" s="5">
+        <v>40</v>
+      </c>
+      <c r="L25">
+        <v>40</v>
+      </c>
+      <c r="M25" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2551,24 +2701,24 @@
         <v>29</v>
       </c>
       <c r="C26" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D26" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G26">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D26" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E26" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F26">
-        <f>RANK(G26,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H26">
         <v>40</v>
@@ -2580,6 +2730,12 @@
         <v>40</v>
       </c>
       <c r="K26" s="5">
+        <v>40</v>
+      </c>
+      <c r="L26">
+        <v>40</v>
+      </c>
+      <c r="M26" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2591,24 +2747,24 @@
         <v>30</v>
       </c>
       <c r="C27" s="4">
+        <f t="shared" si="8"/>
+        <v>63.492063492063494</v>
+      </c>
+      <c r="D27" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D27" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E27" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F27">
-        <f>RANK(G27,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="H27">
         <v>40</v>
@@ -2621,6 +2777,12 @@
       </c>
       <c r="K27" s="5">
         <v>40</v>
+      </c>
+      <c r="L27">
+        <v>40</v>
+      </c>
+      <c r="M27" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:219" x14ac:dyDescent="0.25">
@@ -2631,24 +2793,24 @@
         <v>31</v>
       </c>
       <c r="C28" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D28" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D28" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E28" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F28">
-        <f>RANK(G28,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H28">
         <v>40</v>
@@ -2660,6 +2822,12 @@
         <v>40</v>
       </c>
       <c r="K28" s="5">
+        <v>40</v>
+      </c>
+      <c r="L28">
+        <v>40</v>
+      </c>
+      <c r="M28" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2671,24 +2839,24 @@
         <v>32</v>
       </c>
       <c r="C29" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D29" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E29" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G29">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D29" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E29" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F29">
-        <f>RANK(G29,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H29">
         <v>40</v>
@@ -2700,6 +2868,12 @@
         <v>40</v>
       </c>
       <c r="K29" s="5">
+        <v>40</v>
+      </c>
+      <c r="L29">
+        <v>40</v>
+      </c>
+      <c r="M29" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2711,24 +2885,24 @@
         <v>33</v>
       </c>
       <c r="C30" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D30" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G30">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D30" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E30" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F30">
-        <f>RANK(G30,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -2740,6 +2914,12 @@
         <v>40</v>
       </c>
       <c r="K30" s="5">
+        <v>40</v>
+      </c>
+      <c r="L30">
+        <v>40</v>
+      </c>
+      <c r="M30" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2751,24 +2931,24 @@
         <v>34</v>
       </c>
       <c r="C31" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D31" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E31" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G31">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D31" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E31" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F31">
-        <f>RANK(G31,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H31">
         <v>40</v>
@@ -2780,6 +2960,12 @@
         <v>40</v>
       </c>
       <c r="K31" s="5">
+        <v>40</v>
+      </c>
+      <c r="L31">
+        <v>40</v>
+      </c>
+      <c r="M31" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2791,24 +2977,24 @@
         <v>35</v>
       </c>
       <c r="C32" s="4">
+        <f t="shared" si="8"/>
+        <v>63.492063492063494</v>
+      </c>
+      <c r="D32" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D32" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E32" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F32">
-        <f>RANK(G32,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="H32">
         <v>40</v>
@@ -2821,6 +3007,12 @@
       </c>
       <c r="K32" s="5">
         <v>40</v>
+      </c>
+      <c r="L32">
+        <v>40</v>
+      </c>
+      <c r="M32" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:243" x14ac:dyDescent="0.25">
@@ -2831,24 +3023,24 @@
         <v>36</v>
       </c>
       <c r="C33" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D33" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G33">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D33" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E33" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F33">
-        <f>RANK(G33,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H33">
         <v>40</v>
@@ -2860,6 +3052,12 @@
         <v>40</v>
       </c>
       <c r="K33" s="5">
+        <v>40</v>
+      </c>
+      <c r="L33">
+        <v>40</v>
+      </c>
+      <c r="M33" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2871,24 +3069,24 @@
         <v>37</v>
       </c>
       <c r="C34" s="4">
+        <f t="shared" si="8"/>
+        <v>63.80952380952381</v>
+      </c>
+      <c r="D34" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="G34">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D34" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E34" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F34">
-        <f>RANK(G34,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="H34">
         <v>40</v>
@@ -2900,6 +3098,12 @@
         <v>40</v>
       </c>
       <c r="K34" s="5">
+        <v>40</v>
+      </c>
+      <c r="L34">
+        <v>40</v>
+      </c>
+      <c r="M34" s="5">
         <v>40</v>
       </c>
     </row>
@@ -2911,24 +3115,24 @@
         <v>38</v>
       </c>
       <c r="C35" s="4">
+        <f t="shared" si="8"/>
+        <v>63.492063492063494</v>
+      </c>
+      <c r="D35" s="4">
+        <f t="shared" si="9"/>
+        <v>60</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="G35">
         <f t="shared" si="7"/>
-        <v>62.539682539682538</v>
-      </c>
-      <c r="D35" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" si="9"/>
-        <v>60</v>
-      </c>
-      <c r="F35">
-        <f>RANK(G35,$G$3:$G$37)</f>
-        <v>2</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="6"/>
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="H35">
         <v>40</v>
@@ -2941,6 +3145,12 @@
       </c>
       <c r="K35" s="5">
         <v>40</v>
+      </c>
+      <c r="L35">
+        <v>40</v>
+      </c>
+      <c r="M35" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:243" x14ac:dyDescent="0.25">
@@ -2951,24 +3161,24 @@
         <v>42</v>
       </c>
       <c r="C36" s="4">
-        <f t="shared" ref="C36" si="10">SUM(H36:BR36)/63+60</f>
-        <v>62.539682539682538</v>
+        <f t="shared" ref="C36" si="11">SUM(H36:BR36)/63+60</f>
+        <v>63.80952380952381</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" ref="D36" si="11">SUM(BS36:EH36)/(131-63)+60</f>
+        <f t="shared" ref="D36" si="12">SUM(BS36:EH36)/(131-63)+60</f>
         <v>60</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" ref="E36" si="12">SUM(EH36:FV36)/36+60</f>
+        <f t="shared" ref="E36" si="13">SUM(EH36:FV36)/36+60</f>
         <v>60</v>
       </c>
       <c r="F36">
-        <f>RANK(G36,$G$3:$G$37)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="G36">
-        <f t="shared" ref="G36" si="13">SUM(H36:AAB36)</f>
-        <v>160</v>
+        <f t="shared" ref="G36" si="14">SUM(H36:AAB36)</f>
+        <v>240</v>
       </c>
       <c r="H36">
         <v>40</v>
@@ -2980,6 +3190,12 @@
         <v>40</v>
       </c>
       <c r="K36" s="5">
+        <v>40</v>
+      </c>
+      <c r="L36">
+        <v>40</v>
+      </c>
+      <c r="M36" s="5">
         <v>40</v>
       </c>
     </row>
@@ -3601,16 +3817,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:QB21 H3:QB3 H4:J36 K22:K36">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F3:F36">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -3631,6 +3837,16 @@
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:QB21 H3:M36">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>

--- a/115 僑生A班.xlsx
+++ b/115 僑生A班.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1524EF83-A700-449D-8891-336C02283850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3933E6B-F563-4D55-AB66-AB78E7EC93D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,15 +23,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>排名</t>
   </si>
@@ -173,6 +170,26 @@
   </si>
   <si>
     <t>class0807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0811</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0812</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0813</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class0814</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -243,20 +260,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -275,9 +290,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -315,9 +330,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -350,26 +365,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,26 +400,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -603,7 +584,8 @@
     <col min="9" max="9" width="12.375" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.75" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.875" bestFit="1" customWidth="1"/>
     <col min="22" max="29" width="4.875" bestFit="1" customWidth="1"/>
     <col min="30" max="31" width="5.875" bestFit="1" customWidth="1"/>
@@ -663,27 +645,27 @@
       </c>
       <c r="M1" s="2">
         <f>MIN(N3:N21)-1</f>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="N1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="O1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="P1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="R1" s="2">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>39</v>
       </c>
       <c r="S1" s="2">
         <f t="shared" si="0"/>
@@ -1425,20 +1407,35 @@
       <c r="L2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="4" t="s">
         <v>43</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:195" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4">
         <f>SUM(H3:BR3)/63+60</f>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D3" s="4">
         <f>SUM(BS3:EH3)/(131-63)+60</f>
@@ -1454,7 +1451,7 @@
       </c>
       <c r="G3">
         <f>SUM(H3:AAB3)</f>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H3">
         <v>40</v>
@@ -1472,6 +1469,21 @@
         <v>40</v>
       </c>
       <c r="M3">
+        <v>40</v>
+      </c>
+      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <v>40</v>
+      </c>
+      <c r="Q3">
+        <v>40</v>
+      </c>
+      <c r="R3">
         <v>40</v>
       </c>
     </row>
@@ -1479,12 +1491,12 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" ref="C4:C22" si="4">SUM(H4:BR4)/63+60</f>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:D22" si="5">SUM(BS4:EH4)/(131-63)+60</f>
@@ -1500,7 +1512,7 @@
       </c>
       <c r="G4">
         <f t="shared" ref="G4:G35" si="7">SUM(H4:AAB4)</f>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -1519,18 +1531,33 @@
       </c>
       <c r="M4">
         <v>20</v>
+      </c>
+      <c r="N4">
+        <v>40</v>
+      </c>
+      <c r="O4">
+        <v>40</v>
+      </c>
+      <c r="P4">
+        <v>40</v>
+      </c>
+      <c r="Q4">
+        <v>40</v>
+      </c>
+      <c r="R4">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:195" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="5"/>
@@ -1546,7 +1573,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H5">
         <v>40</v>
@@ -1564,6 +1591,21 @@
         <v>40</v>
       </c>
       <c r="M5">
+        <v>40</v>
+      </c>
+      <c r="N5">
+        <v>40</v>
+      </c>
+      <c r="O5">
+        <v>40</v>
+      </c>
+      <c r="P5">
+        <v>40</v>
+      </c>
+      <c r="Q5">
+        <v>40</v>
+      </c>
+      <c r="R5">
         <v>40</v>
       </c>
     </row>
@@ -1571,12 +1613,12 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="5"/>
@@ -1592,7 +1634,7 @@
       </c>
       <c r="G6">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H6">
         <v>40</v>
@@ -1610,6 +1652,21 @@
         <v>40</v>
       </c>
       <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>40</v>
+      </c>
+      <c r="O6">
+        <v>40</v>
+      </c>
+      <c r="P6">
+        <v>40</v>
+      </c>
+      <c r="Q6">
+        <v>40</v>
+      </c>
+      <c r="R6">
         <v>40</v>
       </c>
     </row>
@@ -1617,12 +1674,12 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4">
         <f t="shared" si="4"/>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="5"/>
@@ -1638,7 +1695,7 @@
       </c>
       <c r="G7">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H7">
         <v>40</v>
@@ -1657,18 +1714,33 @@
       </c>
       <c r="M7">
         <v>20</v>
+      </c>
+      <c r="N7">
+        <v>40</v>
+      </c>
+      <c r="O7">
+        <v>40</v>
+      </c>
+      <c r="P7">
+        <v>40</v>
+      </c>
+      <c r="Q7">
+        <v>40</v>
+      </c>
+      <c r="R7">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:195" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D8" s="4">
         <f t="shared" si="5"/>
@@ -1684,7 +1756,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H8">
         <v>40</v>
@@ -1702,6 +1774,21 @@
         <v>40</v>
       </c>
       <c r="M8">
+        <v>40</v>
+      </c>
+      <c r="N8">
+        <v>40</v>
+      </c>
+      <c r="O8">
+        <v>40</v>
+      </c>
+      <c r="P8">
+        <v>40</v>
+      </c>
+      <c r="Q8">
+        <v>40</v>
+      </c>
+      <c r="R8">
         <v>40</v>
       </c>
     </row>
@@ -1709,12 +1796,12 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D9" s="4">
         <f t="shared" si="5"/>
@@ -1730,7 +1817,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -1748,6 +1835,21 @@
         <v>40</v>
       </c>
       <c r="M9">
+        <v>40</v>
+      </c>
+      <c r="N9">
+        <v>40</v>
+      </c>
+      <c r="O9">
+        <v>40</v>
+      </c>
+      <c r="P9">
+        <v>40</v>
+      </c>
+      <c r="Q9">
+        <v>40</v>
+      </c>
+      <c r="R9">
         <v>40</v>
       </c>
     </row>
@@ -1755,12 +1857,12 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="5"/>
@@ -1776,7 +1878,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H10">
         <v>40</v>
@@ -1794,6 +1896,21 @@
         <v>40</v>
       </c>
       <c r="M10">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>40</v>
+      </c>
+      <c r="O10">
+        <v>40</v>
+      </c>
+      <c r="P10">
+        <v>40</v>
+      </c>
+      <c r="Q10">
+        <v>40</v>
+      </c>
+      <c r="R10">
         <v>40</v>
       </c>
     </row>
@@ -1801,12 +1918,12 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D11" s="4">
         <f t="shared" si="5"/>
@@ -1822,7 +1939,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -1840,6 +1957,21 @@
         <v>40</v>
       </c>
       <c r="M11">
+        <v>40</v>
+      </c>
+      <c r="N11">
+        <v>40</v>
+      </c>
+      <c r="O11">
+        <v>40</v>
+      </c>
+      <c r="P11">
+        <v>40</v>
+      </c>
+      <c r="Q11">
+        <v>40</v>
+      </c>
+      <c r="R11">
         <v>40</v>
       </c>
     </row>
@@ -1847,12 +1979,12 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D12" s="4">
         <f t="shared" si="5"/>
@@ -1868,7 +2000,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H12">
         <v>40</v>
@@ -1886,6 +2018,21 @@
         <v>40</v>
       </c>
       <c r="M12">
+        <v>40</v>
+      </c>
+      <c r="N12">
+        <v>40</v>
+      </c>
+      <c r="O12">
+        <v>40</v>
+      </c>
+      <c r="P12">
+        <v>40</v>
+      </c>
+      <c r="Q12">
+        <v>40</v>
+      </c>
+      <c r="R12">
         <v>40</v>
       </c>
     </row>
@@ -1893,12 +2040,12 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D13" s="4">
         <f t="shared" si="5"/>
@@ -1914,7 +2061,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H13">
         <v>40</v>
@@ -1932,6 +2079,21 @@
         <v>40</v>
       </c>
       <c r="M13">
+        <v>40</v>
+      </c>
+      <c r="N13">
+        <v>40</v>
+      </c>
+      <c r="O13">
+        <v>40</v>
+      </c>
+      <c r="P13">
+        <v>40</v>
+      </c>
+      <c r="Q13">
+        <v>40</v>
+      </c>
+      <c r="R13">
         <v>40</v>
       </c>
     </row>
@@ -1939,12 +2101,12 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" si="5"/>
@@ -1960,7 +2122,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H14">
         <v>40</v>
@@ -1978,6 +2140,21 @@
         <v>40</v>
       </c>
       <c r="M14">
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <v>40</v>
+      </c>
+      <c r="O14">
+        <v>40</v>
+      </c>
+      <c r="P14">
+        <v>40</v>
+      </c>
+      <c r="Q14">
+        <v>40</v>
+      </c>
+      <c r="R14">
         <v>40</v>
       </c>
     </row>
@@ -1985,12 +2162,12 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D15" s="4">
         <f t="shared" si="5"/>
@@ -2006,7 +2183,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H15">
         <v>40</v>
@@ -2024,6 +2201,21 @@
         <v>40</v>
       </c>
       <c r="M15">
+        <v>40</v>
+      </c>
+      <c r="N15">
+        <v>40</v>
+      </c>
+      <c r="O15">
+        <v>40</v>
+      </c>
+      <c r="P15">
+        <v>40</v>
+      </c>
+      <c r="Q15">
+        <v>40</v>
+      </c>
+      <c r="R15">
         <v>40</v>
       </c>
     </row>
@@ -2031,12 +2223,12 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D16" s="4">
         <f t="shared" si="5"/>
@@ -2052,7 +2244,7 @@
       </c>
       <c r="G16">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H16">
         <v>40</v>
@@ -2070,6 +2262,21 @@
         <v>40</v>
       </c>
       <c r="M16">
+        <v>40</v>
+      </c>
+      <c r="N16">
+        <v>40</v>
+      </c>
+      <c r="O16">
+        <v>40</v>
+      </c>
+      <c r="P16">
+        <v>40</v>
+      </c>
+      <c r="Q16">
+        <v>40</v>
+      </c>
+      <c r="R16">
         <v>40</v>
       </c>
     </row>
@@ -2077,12 +2284,12 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D17" s="4">
         <f t="shared" si="5"/>
@@ -2098,7 +2305,7 @@
       </c>
       <c r="G17">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -2116,6 +2323,21 @@
         <v>40</v>
       </c>
       <c r="M17">
+        <v>40</v>
+      </c>
+      <c r="N17">
+        <v>40</v>
+      </c>
+      <c r="O17">
+        <v>40</v>
+      </c>
+      <c r="P17">
+        <v>40</v>
+      </c>
+      <c r="Q17">
+        <v>40</v>
+      </c>
+      <c r="R17">
         <v>40</v>
       </c>
     </row>
@@ -2123,12 +2345,12 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C18" s="4">
         <f t="shared" si="4"/>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D18" s="4">
         <f t="shared" si="5"/>
@@ -2144,7 +2366,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H18">
         <v>40</v>
@@ -2163,18 +2385,33 @@
       </c>
       <c r="M18">
         <v>20</v>
+      </c>
+      <c r="N18">
+        <v>40</v>
+      </c>
+      <c r="O18">
+        <v>40</v>
+      </c>
+      <c r="P18">
+        <v>40</v>
+      </c>
+      <c r="Q18">
+        <v>40</v>
+      </c>
+      <c r="R18">
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:219" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D19" s="4">
         <f t="shared" si="5"/>
@@ -2190,7 +2427,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -2208,6 +2445,21 @@
         <v>40</v>
       </c>
       <c r="M19">
+        <v>40</v>
+      </c>
+      <c r="N19">
+        <v>40</v>
+      </c>
+      <c r="O19">
+        <v>40</v>
+      </c>
+      <c r="P19">
+        <v>40</v>
+      </c>
+      <c r="Q19">
+        <v>40</v>
+      </c>
+      <c r="R19">
         <v>40</v>
       </c>
     </row>
@@ -2215,12 +2467,12 @@
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D20" s="4">
         <f t="shared" si="5"/>
@@ -2236,7 +2488,7 @@
       </c>
       <c r="G20">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -2254,6 +2506,21 @@
         <v>40</v>
       </c>
       <c r="M20">
+        <v>40</v>
+      </c>
+      <c r="N20">
+        <v>40</v>
+      </c>
+      <c r="O20">
+        <v>40</v>
+      </c>
+      <c r="P20">
+        <v>40</v>
+      </c>
+      <c r="Q20">
+        <v>40</v>
+      </c>
+      <c r="R20">
         <v>40</v>
       </c>
     </row>
@@ -2261,12 +2528,12 @@
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D21" s="4">
         <f t="shared" si="5"/>
@@ -2282,7 +2549,7 @@
       </c>
       <c r="G21">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -2300,6 +2567,21 @@
         <v>40</v>
       </c>
       <c r="M21">
+        <v>40</v>
+      </c>
+      <c r="N21">
+        <v>40</v>
+      </c>
+      <c r="O21">
+        <v>40</v>
+      </c>
+      <c r="P21">
+        <v>40</v>
+      </c>
+      <c r="Q21">
+        <v>40</v>
+      </c>
+      <c r="R21">
         <v>40</v>
       </c>
     </row>
@@ -2307,12 +2589,12 @@
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C22" s="4">
         <f t="shared" si="4"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D22" s="4">
         <f t="shared" si="5"/>
@@ -2328,7 +2610,7 @@
       </c>
       <c r="G22">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -2339,232 +2621,242 @@
       <c r="J22">
         <v>40</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22">
         <v>40</v>
       </c>
       <c r="L22">
         <v>40</v>
       </c>
-      <c r="M22" s="5">
-        <v>40</v>
-      </c>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5"/>
-      <c r="AJ22" s="5"/>
-      <c r="AK22" s="5"/>
-      <c r="AL22" s="5"/>
-      <c r="AM22" s="5"/>
-      <c r="AN22" s="5"/>
-      <c r="AO22" s="5"/>
-      <c r="AP22" s="5"/>
-      <c r="AQ22" s="5"/>
-      <c r="AR22" s="5"/>
-      <c r="AS22" s="5"/>
-      <c r="AT22" s="5"/>
-      <c r="AU22" s="5"/>
-      <c r="AV22" s="5"/>
-      <c r="AW22" s="5"/>
-      <c r="AX22" s="5"/>
-      <c r="AY22" s="5"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-      <c r="CV22" s="5"/>
-      <c r="CW22" s="5"/>
-      <c r="CX22" s="5"/>
-      <c r="CY22" s="5"/>
-      <c r="CZ22" s="5"/>
-      <c r="DA22" s="5"/>
-      <c r="DB22" s="5"/>
-      <c r="DC22" s="5"/>
-      <c r="DD22" s="5"/>
-      <c r="DE22" s="5"/>
-      <c r="DF22" s="5"/>
-      <c r="DG22" s="5"/>
-      <c r="DH22" s="5"/>
-      <c r="DI22" s="5"/>
-      <c r="DJ22" s="5"/>
-      <c r="DK22" s="5"/>
-      <c r="DL22" s="5"/>
-      <c r="DM22" s="5"/>
-      <c r="DN22" s="5"/>
-      <c r="DO22" s="5"/>
-      <c r="DP22" s="5"/>
-      <c r="DQ22" s="5"/>
-      <c r="DR22" s="5"/>
-      <c r="DS22" s="5"/>
-      <c r="DT22" s="5"/>
-      <c r="DU22" s="5"/>
-      <c r="DV22" s="5"/>
-      <c r="DW22" s="5"/>
-      <c r="DX22" s="5"/>
-      <c r="DY22" s="5"/>
-      <c r="DZ22" s="5"/>
-      <c r="EA22" s="5"/>
-      <c r="EB22" s="5"/>
-      <c r="EC22" s="5"/>
-      <c r="ED22" s="5"/>
-      <c r="EE22" s="5"/>
-      <c r="EF22" s="5"/>
-      <c r="EG22" s="5"/>
-      <c r="EH22" s="5"/>
-      <c r="EI22" s="5"/>
-      <c r="EJ22" s="5"/>
-      <c r="EK22" s="5"/>
-      <c r="EL22" s="5"/>
-      <c r="EM22" s="5"/>
-      <c r="EN22" s="5"/>
-      <c r="EO22" s="5"/>
-      <c r="EP22" s="5"/>
-      <c r="EQ22" s="5"/>
-      <c r="ER22" s="5"/>
-      <c r="ES22" s="5"/>
-      <c r="ET22" s="5"/>
-      <c r="EU22" s="5"/>
-      <c r="EV22" s="5"/>
-      <c r="EW22" s="5"/>
-      <c r="EX22" s="5"/>
-      <c r="EY22" s="5"/>
-      <c r="EZ22" s="5"/>
-      <c r="FA22" s="5"/>
-      <c r="FB22" s="5"/>
-      <c r="FC22" s="5"/>
-      <c r="FD22" s="5"/>
-      <c r="FE22" s="5"/>
-      <c r="FF22" s="5"/>
-      <c r="FG22" s="5"/>
-      <c r="FH22" s="5"/>
-      <c r="FI22" s="5"/>
-      <c r="FJ22" s="5"/>
-      <c r="FK22" s="5"/>
-      <c r="FL22" s="5"/>
-      <c r="FM22" s="5"/>
-      <c r="FN22" s="5"/>
-      <c r="FO22" s="5"/>
-      <c r="FP22" s="5"/>
-      <c r="FQ22" s="5"/>
-      <c r="FR22" s="5"/>
-      <c r="FS22" s="5"/>
-      <c r="FT22" s="5"/>
-      <c r="FU22" s="5"/>
-      <c r="FV22" s="5"/>
-      <c r="FW22" s="5"/>
-      <c r="FX22" s="5"/>
-      <c r="FY22" s="5"/>
-      <c r="FZ22" s="5"/>
-      <c r="GA22" s="5"/>
-      <c r="GB22" s="5"/>
-      <c r="GC22" s="5"/>
-      <c r="GD22" s="5"/>
-      <c r="GE22" s="5"/>
-      <c r="GF22" s="5"/>
-      <c r="GG22" s="5"/>
-      <c r="GH22" s="5"/>
-      <c r="GI22" s="5"/>
-      <c r="GJ22" s="5"/>
-      <c r="GK22" s="5"/>
-      <c r="GL22" s="5"/>
-      <c r="GM22" s="5"/>
-      <c r="GN22" s="5"/>
-      <c r="GO22" s="5"/>
-      <c r="GP22" s="5"/>
-      <c r="GQ22" s="5"/>
-      <c r="GR22" s="5"/>
-      <c r="GS22" s="5"/>
-      <c r="GT22" s="5"/>
-      <c r="GU22" s="5"/>
-      <c r="GV22" s="5"/>
-      <c r="GW22" s="5"/>
-      <c r="GX22" s="5"/>
-      <c r="GY22" s="5"/>
-      <c r="GZ22" s="5"/>
-      <c r="HA22" s="5"/>
-      <c r="HB22" s="5"/>
-      <c r="HC22" s="5"/>
-      <c r="HD22" s="5"/>
-      <c r="HE22" s="5"/>
-      <c r="HF22" s="5"/>
-      <c r="HG22" s="5"/>
-      <c r="HH22" s="5"/>
-      <c r="HI22" s="5"/>
-      <c r="HJ22" s="5"/>
-      <c r="HK22" s="5"/>
+      <c r="M22">
+        <v>40</v>
+      </c>
+      <c r="N22">
+        <v>40</v>
+      </c>
+      <c r="O22">
+        <v>40</v>
+      </c>
+      <c r="P22">
+        <v>40</v>
+      </c>
+      <c r="Q22">
+        <v>40</v>
+      </c>
+      <c r="R22">
+        <v>40</v>
+      </c>
+      <c r="S22"/>
+      <c r="T22"/>
+      <c r="U22"/>
+      <c r="V22"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+      <c r="AG22"/>
+      <c r="AH22"/>
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+      <c r="AR22"/>
+      <c r="AS22"/>
+      <c r="AT22"/>
+      <c r="AU22"/>
+      <c r="AV22"/>
+      <c r="AW22"/>
+      <c r="AX22"/>
+      <c r="AY22"/>
+      <c r="AZ22"/>
+      <c r="BA22"/>
+      <c r="BB22"/>
+      <c r="BC22"/>
+      <c r="BD22"/>
+      <c r="BE22"/>
+      <c r="BF22"/>
+      <c r="BG22"/>
+      <c r="BH22"/>
+      <c r="BI22"/>
+      <c r="BJ22"/>
+      <c r="BK22"/>
+      <c r="BL22"/>
+      <c r="BM22"/>
+      <c r="BN22"/>
+      <c r="BO22"/>
+      <c r="BP22"/>
+      <c r="BQ22"/>
+      <c r="BR22"/>
+      <c r="BS22"/>
+      <c r="BT22"/>
+      <c r="BU22"/>
+      <c r="BV22"/>
+      <c r="BW22"/>
+      <c r="BX22"/>
+      <c r="BY22"/>
+      <c r="BZ22"/>
+      <c r="CA22"/>
+      <c r="CB22"/>
+      <c r="CC22"/>
+      <c r="CD22"/>
+      <c r="CE22"/>
+      <c r="CF22"/>
+      <c r="CG22"/>
+      <c r="CH22"/>
+      <c r="CI22"/>
+      <c r="CJ22"/>
+      <c r="CK22"/>
+      <c r="CL22"/>
+      <c r="CM22"/>
+      <c r="CN22"/>
+      <c r="CO22"/>
+      <c r="CP22"/>
+      <c r="CQ22"/>
+      <c r="CR22"/>
+      <c r="CS22"/>
+      <c r="CT22"/>
+      <c r="CU22"/>
+      <c r="CV22"/>
+      <c r="CW22"/>
+      <c r="CX22"/>
+      <c r="CY22"/>
+      <c r="CZ22"/>
+      <c r="DA22"/>
+      <c r="DB22"/>
+      <c r="DC22"/>
+      <c r="DD22"/>
+      <c r="DE22"/>
+      <c r="DF22"/>
+      <c r="DG22"/>
+      <c r="DH22"/>
+      <c r="DI22"/>
+      <c r="DJ22"/>
+      <c r="DK22"/>
+      <c r="DL22"/>
+      <c r="DM22"/>
+      <c r="DN22"/>
+      <c r="DO22"/>
+      <c r="DP22"/>
+      <c r="DQ22"/>
+      <c r="DR22"/>
+      <c r="DS22"/>
+      <c r="DT22"/>
+      <c r="DU22"/>
+      <c r="DV22"/>
+      <c r="DW22"/>
+      <c r="DX22"/>
+      <c r="DY22"/>
+      <c r="DZ22"/>
+      <c r="EA22"/>
+      <c r="EB22"/>
+      <c r="EC22"/>
+      <c r="ED22"/>
+      <c r="EE22"/>
+      <c r="EF22"/>
+      <c r="EG22"/>
+      <c r="EH22"/>
+      <c r="EI22"/>
+      <c r="EJ22"/>
+      <c r="EK22"/>
+      <c r="EL22"/>
+      <c r="EM22"/>
+      <c r="EN22"/>
+      <c r="EO22"/>
+      <c r="EP22"/>
+      <c r="EQ22"/>
+      <c r="ER22"/>
+      <c r="ES22"/>
+      <c r="ET22"/>
+      <c r="EU22"/>
+      <c r="EV22"/>
+      <c r="EW22"/>
+      <c r="EX22"/>
+      <c r="EY22"/>
+      <c r="EZ22"/>
+      <c r="FA22"/>
+      <c r="FB22"/>
+      <c r="FC22"/>
+      <c r="FD22"/>
+      <c r="FE22"/>
+      <c r="FF22"/>
+      <c r="FG22"/>
+      <c r="FH22"/>
+      <c r="FI22"/>
+      <c r="FJ22"/>
+      <c r="FK22"/>
+      <c r="FL22"/>
+      <c r="FM22"/>
+      <c r="FN22"/>
+      <c r="FO22"/>
+      <c r="FP22"/>
+      <c r="FQ22"/>
+      <c r="FR22"/>
+      <c r="FS22"/>
+      <c r="FT22"/>
+      <c r="FU22"/>
+      <c r="FV22"/>
+      <c r="FW22"/>
+      <c r="FX22"/>
+      <c r="FY22"/>
+      <c r="FZ22"/>
+      <c r="GA22"/>
+      <c r="GB22"/>
+      <c r="GC22"/>
+      <c r="GD22"/>
+      <c r="GE22"/>
+      <c r="GF22"/>
+      <c r="GG22"/>
+      <c r="GH22"/>
+      <c r="GI22"/>
+      <c r="GJ22"/>
+      <c r="GK22"/>
+      <c r="GL22"/>
+      <c r="GM22"/>
+      <c r="GN22"/>
+      <c r="GO22"/>
+      <c r="GP22"/>
+      <c r="GQ22"/>
+      <c r="GR22"/>
+      <c r="GS22"/>
+      <c r="GT22"/>
+      <c r="GU22"/>
+      <c r="GV22"/>
+      <c r="GW22"/>
+      <c r="GX22"/>
+      <c r="GY22"/>
+      <c r="GZ22"/>
+      <c r="HA22"/>
+      <c r="HB22"/>
+      <c r="HC22"/>
+      <c r="HD22"/>
+      <c r="HE22"/>
+      <c r="HF22"/>
+      <c r="HG22"/>
+      <c r="HH22"/>
+      <c r="HI22"/>
+      <c r="HJ22"/>
+      <c r="HK22"/>
     </row>
     <row r="23" spans="1:219" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="4">
         <f t="shared" ref="C23:C35" si="8">SUM(H23:BR23)/63+60</f>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D23" s="4">
         <f t="shared" ref="D23:D35" si="9">SUM(BS23:EH23)/(131-63)+60</f>
@@ -2580,7 +2872,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -2591,13 +2883,28 @@
       <c r="J23">
         <v>40</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23">
         <v>40</v>
       </c>
       <c r="L23">
         <v>40</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23">
+        <v>40</v>
+      </c>
+      <c r="N23">
+        <v>40</v>
+      </c>
+      <c r="O23">
+        <v>40</v>
+      </c>
+      <c r="P23">
+        <v>40</v>
+      </c>
+      <c r="Q23">
+        <v>40</v>
+      </c>
+      <c r="R23">
         <v>40</v>
       </c>
     </row>
@@ -2605,12 +2912,12 @@
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D24" s="4">
         <f t="shared" si="9"/>
@@ -2626,7 +2933,7 @@
       </c>
       <c r="G24">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H24">
         <v>40</v>
@@ -2637,13 +2944,28 @@
       <c r="J24">
         <v>40</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24">
         <v>40</v>
       </c>
       <c r="L24">
         <v>40</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24">
+        <v>40</v>
+      </c>
+      <c r="N24">
+        <v>40</v>
+      </c>
+      <c r="O24">
+        <v>40</v>
+      </c>
+      <c r="P24">
+        <v>40</v>
+      </c>
+      <c r="Q24">
+        <v>40</v>
+      </c>
+      <c r="R24">
         <v>40</v>
       </c>
     </row>
@@ -2651,12 +2973,12 @@
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D25" s="4">
         <f t="shared" si="9"/>
@@ -2672,7 +2994,7 @@
       </c>
       <c r="G25">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H25">
         <v>40</v>
@@ -2683,13 +3005,28 @@
       <c r="J25">
         <v>40</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25">
         <v>40</v>
       </c>
       <c r="L25">
         <v>40</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25">
+        <v>40</v>
+      </c>
+      <c r="N25">
+        <v>40</v>
+      </c>
+      <c r="O25">
+        <v>40</v>
+      </c>
+      <c r="P25">
+        <v>40</v>
+      </c>
+      <c r="Q25">
+        <v>40</v>
+      </c>
+      <c r="R25">
         <v>40</v>
       </c>
     </row>
@@ -2697,12 +3034,12 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D26" s="4">
         <f t="shared" si="9"/>
@@ -2718,7 +3055,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H26">
         <v>40</v>
@@ -2729,13 +3066,28 @@
       <c r="J26">
         <v>40</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26">
         <v>40</v>
       </c>
       <c r="L26">
         <v>40</v>
       </c>
-      <c r="M26" s="5">
+      <c r="M26">
+        <v>40</v>
+      </c>
+      <c r="N26">
+        <v>40</v>
+      </c>
+      <c r="O26">
+        <v>40</v>
+      </c>
+      <c r="P26">
+        <v>40</v>
+      </c>
+      <c r="Q26">
+        <v>40</v>
+      </c>
+      <c r="R26">
         <v>40</v>
       </c>
     </row>
@@ -2743,12 +3095,12 @@
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="4">
         <f t="shared" si="8"/>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D27" s="4">
         <f t="shared" si="9"/>
@@ -2764,7 +3116,7 @@
       </c>
       <c r="G27">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H27">
         <v>40</v>
@@ -2775,26 +3127,41 @@
       <c r="J27">
         <v>40</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27">
         <v>40</v>
       </c>
       <c r="L27">
         <v>40</v>
       </c>
-      <c r="M27" s="5">
+      <c r="M27">
         <v>20</v>
+      </c>
+      <c r="N27">
+        <v>40</v>
+      </c>
+      <c r="O27">
+        <v>40</v>
+      </c>
+      <c r="P27">
+        <v>40</v>
+      </c>
+      <c r="Q27">
+        <v>40</v>
+      </c>
+      <c r="R27">
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:219" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D28" s="4">
         <f t="shared" si="9"/>
@@ -2810,7 +3177,7 @@
       </c>
       <c r="G28">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H28">
         <v>40</v>
@@ -2821,13 +3188,28 @@
       <c r="J28">
         <v>40</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28">
         <v>40</v>
       </c>
       <c r="L28">
         <v>40</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28">
+        <v>40</v>
+      </c>
+      <c r="N28">
+        <v>40</v>
+      </c>
+      <c r="O28">
+        <v>40</v>
+      </c>
+      <c r="P28">
+        <v>40</v>
+      </c>
+      <c r="Q28">
+        <v>40</v>
+      </c>
+      <c r="R28">
         <v>40</v>
       </c>
     </row>
@@ -2835,12 +3217,12 @@
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C29" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D29" s="4">
         <f t="shared" si="9"/>
@@ -2856,7 +3238,7 @@
       </c>
       <c r="G29">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H29">
         <v>40</v>
@@ -2867,13 +3249,28 @@
       <c r="J29">
         <v>40</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29">
         <v>40</v>
       </c>
       <c r="L29">
         <v>40</v>
       </c>
-      <c r="M29" s="5">
+      <c r="M29">
+        <v>40</v>
+      </c>
+      <c r="N29">
+        <v>40</v>
+      </c>
+      <c r="O29">
+        <v>40</v>
+      </c>
+      <c r="P29">
+        <v>40</v>
+      </c>
+      <c r="Q29">
+        <v>40</v>
+      </c>
+      <c r="R29">
         <v>40</v>
       </c>
     </row>
@@ -2881,12 +3278,12 @@
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="9"/>
@@ -2902,7 +3299,7 @@
       </c>
       <c r="G30">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H30">
         <v>40</v>
@@ -2913,13 +3310,28 @@
       <c r="J30">
         <v>40</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30">
         <v>40</v>
       </c>
       <c r="L30">
         <v>40</v>
       </c>
-      <c r="M30" s="5">
+      <c r="M30">
+        <v>40</v>
+      </c>
+      <c r="N30">
+        <v>40</v>
+      </c>
+      <c r="O30">
+        <v>40</v>
+      </c>
+      <c r="P30">
+        <v>40</v>
+      </c>
+      <c r="Q30">
+        <v>40</v>
+      </c>
+      <c r="R30">
         <v>40</v>
       </c>
     </row>
@@ -2927,12 +3339,12 @@
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="9"/>
@@ -2948,7 +3360,7 @@
       </c>
       <c r="G31">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H31">
         <v>40</v>
@@ -2959,13 +3371,28 @@
       <c r="J31">
         <v>40</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31">
         <v>40</v>
       </c>
       <c r="L31">
         <v>40</v>
       </c>
-      <c r="M31" s="5">
+      <c r="M31">
+        <v>40</v>
+      </c>
+      <c r="N31">
+        <v>40</v>
+      </c>
+      <c r="O31">
+        <v>40</v>
+      </c>
+      <c r="P31">
+        <v>40</v>
+      </c>
+      <c r="Q31">
+        <v>40</v>
+      </c>
+      <c r="R31">
         <v>40</v>
       </c>
     </row>
@@ -2973,12 +3400,12 @@
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="4">
         <f t="shared" si="8"/>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D32" s="4">
         <f t="shared" si="9"/>
@@ -2994,7 +3421,7 @@
       </c>
       <c r="G32">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H32">
         <v>40</v>
@@ -3005,26 +3432,41 @@
       <c r="J32">
         <v>40</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32">
         <v>40</v>
       </c>
       <c r="L32">
         <v>40</v>
       </c>
-      <c r="M32" s="5">
+      <c r="M32">
         <v>20</v>
+      </c>
+      <c r="N32">
+        <v>40</v>
+      </c>
+      <c r="O32">
+        <v>40</v>
+      </c>
+      <c r="P32">
+        <v>40</v>
+      </c>
+      <c r="Q32">
+        <v>40</v>
+      </c>
+      <c r="R32">
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:243" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D33" s="4">
         <f t="shared" si="9"/>
@@ -3040,7 +3482,7 @@
       </c>
       <c r="G33">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H33">
         <v>40</v>
@@ -3051,13 +3493,28 @@
       <c r="J33">
         <v>40</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33">
         <v>40</v>
       </c>
       <c r="L33">
         <v>40</v>
       </c>
-      <c r="M33" s="5">
+      <c r="M33">
+        <v>40</v>
+      </c>
+      <c r="N33">
+        <v>40</v>
+      </c>
+      <c r="O33">
+        <v>40</v>
+      </c>
+      <c r="P33">
+        <v>40</v>
+      </c>
+      <c r="Q33">
+        <v>40</v>
+      </c>
+      <c r="R33">
         <v>40</v>
       </c>
     </row>
@@ -3065,12 +3522,12 @@
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="4">
         <f t="shared" si="8"/>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D34" s="4">
         <f t="shared" si="9"/>
@@ -3086,7 +3543,7 @@
       </c>
       <c r="G34">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H34">
         <v>40</v>
@@ -3097,13 +3554,28 @@
       <c r="J34">
         <v>40</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34">
         <v>40</v>
       </c>
       <c r="L34">
         <v>40</v>
       </c>
-      <c r="M34" s="5">
+      <c r="M34">
+        <v>40</v>
+      </c>
+      <c r="N34">
+        <v>40</v>
+      </c>
+      <c r="O34">
+        <v>40</v>
+      </c>
+      <c r="P34">
+        <v>40</v>
+      </c>
+      <c r="Q34">
+        <v>40</v>
+      </c>
+      <c r="R34">
         <v>40</v>
       </c>
     </row>
@@ -3111,12 +3583,12 @@
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="4">
         <f t="shared" si="8"/>
-        <v>63.492063492063494</v>
+        <v>66.666666666666671</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="9"/>
@@ -3132,7 +3604,7 @@
       </c>
       <c r="G35">
         <f t="shared" si="7"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H35">
         <v>40</v>
@@ -3143,26 +3615,41 @@
       <c r="J35">
         <v>40</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35">
         <v>40</v>
       </c>
       <c r="L35">
         <v>40</v>
       </c>
-      <c r="M35" s="5">
+      <c r="M35">
         <v>20</v>
+      </c>
+      <c r="N35">
+        <v>40</v>
+      </c>
+      <c r="O35">
+        <v>40</v>
+      </c>
+      <c r="P35">
+        <v>40</v>
+      </c>
+      <c r="Q35">
+        <v>40</v>
+      </c>
+      <c r="R35">
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:243" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="4">
         <f t="shared" ref="C36" si="11">SUM(H36:BR36)/63+60</f>
-        <v>63.80952380952381</v>
+        <v>66.984126984126988</v>
       </c>
       <c r="D36" s="4">
         <f t="shared" ref="D36" si="12">SUM(BS36:EH36)/(131-63)+60</f>
@@ -3178,7 +3665,7 @@
       </c>
       <c r="G36">
         <f t="shared" ref="G36" si="14">SUM(H36:AAB36)</f>
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="H36">
         <v>40</v>
@@ -3189,13 +3676,28 @@
       <c r="J36">
         <v>40</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36">
         <v>40</v>
       </c>
       <c r="L36">
         <v>40</v>
       </c>
-      <c r="M36" s="5">
+      <c r="M36">
+        <v>40</v>
+      </c>
+      <c r="N36">
+        <v>40</v>
+      </c>
+      <c r="O36">
+        <v>40</v>
+      </c>
+      <c r="P36">
+        <v>40</v>
+      </c>
+      <c r="Q36">
+        <v>40</v>
+      </c>
+      <c r="R36">
         <v>40</v>
       </c>
     </row>
@@ -3803,6 +4305,30 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C3:E36">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F36">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G3:G36">
     <cfRule type="dataBar" priority="4">
       <dataBar>
@@ -3817,31 +4343,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F36">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:E36">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:QB21 H3:M36">
+  <conditionalFormatting sqref="H3:M36 N3:QB3 S4:QB21 N4:R36">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
